--- a/Paper2_Package/03_RESULTS/Task4_drug_coverage/task4_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task4_drug_coverage/task4_supporting.xlsx
@@ -3576,7 +3576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D727"/>
+  <dimension ref="A1:D696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3908,39 +3908,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L-ALANINE</t>
+          <t>RIBOFLAVIN 5'-PHOSPHATE</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>0.538</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RIBOFLAVIN 5'-PHOSPHATE</t>
+          <t>COENZYME_A</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>0.636</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MIBEFRADIL</t>
+          <t>CHEMBL2021342</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -3956,39 +3956,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHEMBL2021342</t>
+          <t>CHEMBL2365712</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D24" t="n">
-        <v>0.545</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHEMBL2365712</t>
+          <t>CHEMBL574817</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MANIDIPINE 6300</t>
+          <t>CHEMBL609728</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -4004,46 +4004,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CHEMBL574817</t>
+          <t>ORNITHINE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
         <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BENIDIPINE</t>
+          <t>RETINOL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D28" t="n">
-        <v>0.462</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHEMBL609728</t>
+          <t>CHEMBL126506</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
         <v>0.5</v>
@@ -4052,14 +4052,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ESTRADIOL CYPIONATE</t>
+          <t>CHEMBL3184454</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
         <v>0.5</v>
@@ -4068,14 +4068,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ESTRADIOL ACETATE</t>
+          <t>CHOLINE</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
         <v>0.5</v>
@@ -4084,302 +4084,302 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BUTABARBITAL</t>
+          <t>CHEMBL1234619</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>0.139</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ESTRADIOL VALERATE</t>
+          <t>CHEMBL140</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ESTRADIOL BENZOATE</t>
+          <t>CHEMBL3185220</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MAGNESIUM SULFATE ANHYDROUS</t>
+          <t>CHEMBL3275971</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="n">
         <v>4</v>
       </c>
-      <c r="C35" t="n">
-        <v>9</v>
-      </c>
       <c r="D35" t="n">
-        <v>0.444</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RETINOL</t>
+          <t>CREATINE</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>0.267</v>
+        <v>0.429</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHEMBL126506</t>
+          <t>CHEMBL7064</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" t="n">
         <v>4</v>
       </c>
-      <c r="C37" t="n">
-        <v>8</v>
-      </c>
       <c r="D37" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CHOLINE SALICYLATE</t>
+          <t>TAURINE</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D38" t="n">
-        <v>0.571</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CHEMBL3184454</t>
+          <t>CHEMBL407009</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CHOLINE</t>
+          <t>SODIUM CARBONATE</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
         <v>4</v>
       </c>
-      <c r="C40" t="n">
-        <v>8</v>
-      </c>
       <c r="D40" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHEMBL1234619</t>
+          <t>CHEMBL445001</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHEMBL140</t>
+          <t>UREA</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHEMBL3185220</t>
+          <t>CHEMBL1080759</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="n">
         <v>3</v>
       </c>
-      <c r="C43" t="n">
-        <v>4</v>
-      </c>
       <c r="D43" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHEMBL3275971</t>
+          <t>CHEMBL1232920</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CREATINE</t>
+          <t>CHEMBL1235255</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
         <v>3</v>
       </c>
-      <c r="C45" t="n">
-        <v>7</v>
-      </c>
       <c r="D45" t="n">
-        <v>0.429</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DEXAMETHASONE ACETATE</t>
+          <t>CHEMBL1235246</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MEDROXYPROGESTERONE ACETATE</t>
+          <t>LITHIUM ION</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CHEMBL7064</t>
+          <t>CHEMBL1235115</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TAURINE</t>
+          <t>CHEMBL388154</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>0.143</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CHEMBL407009</t>
+          <t>CHEMBL394875</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
@@ -4388,62 +4388,62 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SODIUM CARBONATE</t>
+          <t>MAGNESIUM ACETATE TETRAHYDRATE</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>0.75</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Lauryldimethylamine N-Oxide</t>
+          <t>CHEMBL38397</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="n">
         <v>3</v>
       </c>
-      <c r="C52" t="n">
-        <v>8</v>
-      </c>
       <c r="D52" t="n">
-        <v>0.375</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHEMBL445001</t>
+          <t>CHEMBL1237210</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="n">
         <v>3</v>
       </c>
-      <c r="C53" t="n">
-        <v>9</v>
-      </c>
       <c r="D53" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>UREA</t>
+          <t>CHEMBL391737</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
@@ -4452,71 +4452,71 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CHEMBL1080759</t>
+          <t>CHEMBL391640</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CHEMBL1232920</t>
+          <t>ALPHA-TOCOPHEROL</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CHEMBL1235255</t>
+          <t>CHEMBL1230790</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHEMBL1235246</t>
+          <t>CHEMBL490225</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CHEMBL1235115</t>
+          <t>CHEMBL383189</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -4532,23 +4532,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CHEMBL388154</t>
+          <t>CHEMBL1207374</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CHEMBL394875</t>
+          <t>CHEMBL1229585</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -4564,39 +4564,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MAGNESIUM ACETATE TETRAHYDRATE</t>
+          <t>CHEMBL486954</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>2</v>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>0.286</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CHEMBL38397</t>
+          <t>CHEMBL1230513</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CHEMBL1237210</t>
+          <t>CHEMBL1230309</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -4612,23 +4612,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CHEMBL391737</t>
+          <t>CHEMBL345292</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CHEMBL391640</t>
+          <t>CHEMBL350239</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -4644,23 +4644,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ALPHA-TOCOPHEROL</t>
+          <t>CHEMBL510038</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>0.25</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CHEMBL1230790</t>
+          <t>CHEMBL1213270</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -4676,39 +4676,39 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CHEMBL490225</t>
+          <t>CHEMBL1213083</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CHEMBL383189</t>
+          <t>CHEMBL1204498</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CHEMBL1207374</t>
+          <t>CHEMBL327715</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4724,71 +4724,71 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CHEMBL1229585</t>
+          <t>CHEMBL146245</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHEMBL486954</t>
+          <t>CHEMBL283807</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D73" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CHEMBL1230513</t>
+          <t>CHEMBL286939</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CHEMBL1230309</t>
+          <t>MAGNESIUM CARBONATE</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D75" t="n">
-        <v>0.667</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CHEMBL345292</t>
+          <t>CHEMBL260629</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -4804,39 +4804,39 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SEGESTERONE ACETATE</t>
+          <t>CHEMBL24683</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>2</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CHEMBL350239</t>
+          <t>CHEMBL1161998</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>2</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CHEMBL510038</t>
+          <t>CHEMBL74078</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4852,23 +4852,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CHEMBL1213270</t>
+          <t>SUCROSE</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CHEMBL1213083</t>
+          <t>SODIUM SULFATE ANHYDROUS</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4884,222 +4884,222 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CHEMBL1204498</t>
+          <t>CHEMBL223026</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CHEMBL327715</t>
+          <t>CHEMBL213907</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D83" t="n">
-        <v>0.667</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CHEMBL146245</t>
+          <t>CHEMBL113690</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LITHIUM CITRATE ANHYDROUS</t>
+          <t>SERINE</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>2</v>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CHEMBL283807</t>
+          <t>CHEMBL21156</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>2</v>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>0.286</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LITHIUM CARBONATE</t>
+          <t>CHEMBL216543</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D87" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CHEMBL286939</t>
+          <t>CHEMBL180792</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MAGNESIUM CARBONATE</t>
+          <t>CHEMBL180517</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>0.286</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CHEMBL260629</t>
+          <t>CHEMBL180071</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CHEMBL24683</t>
+          <t>CHEMBL96433</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CHEMBL1161998</t>
+          <t>CHEMBL193676</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>2</v>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CHEMBL74078</t>
+          <t>TOCOPHEROL ACETATE</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>2</v>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D93" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SUCROSE</t>
+          <t>CHEMBL96862</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SODIUM SULFATE ANHYDROUS</t>
+          <t>CHEMBL95700</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
@@ -5108,14 +5108,14 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CHEMBL223026</t>
+          <t>CHEMBL93560</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
@@ -5124,30 +5124,30 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CHEMBL213907</t>
+          <t>CHEMBL93647</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>0.111</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CHEMBL113690</t>
+          <t>CHEMBL94061</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
@@ -5156,30 +5156,30 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SERINE</t>
+          <t>CHEMBL94277</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>0.286</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MAGNESIUM SALICYLATE</t>
+          <t>CHEMBL106708</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
         <v>1</v>
@@ -5188,62 +5188,62 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CHEMBL21156</t>
+          <t>CHEMBL107316</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CHEMBL216543</t>
+          <t>CHEMBL191275</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>HYDROCORTISONE ACETATE</t>
+          <t>CHEMBL192894</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CHEMBL180792</t>
+          <t>CHEMBL193233</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
@@ -5252,14 +5252,14 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CHEMBL180517</t>
+          <t>CHEMBL194176</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
@@ -5268,14 +5268,14 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CHEMBL180071</t>
+          <t>CHEMBL194805</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
@@ -5284,55 +5284,55 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CHEMBL96433</t>
+          <t>CHEMBL194911</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CHEMBL193676</t>
+          <t>CHEMBL204997</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C108" t="n">
         <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TOCOPHEROL ACETATE</t>
+          <t>CHEMBL205437</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CHEMBL96862</t>
+          <t>CHEMBL205786</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -5348,7 +5348,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CHEMBL95700</t>
+          <t>CHEMBL200255</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -5364,7 +5364,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CHEMBL93560</t>
+          <t>CHEMBL200469</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -5380,7 +5380,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CHEMBL93647</t>
+          <t>CHEMBL200495</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -5396,7 +5396,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CHEMBL94061</t>
+          <t>CHEMBL201880</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -5412,7 +5412,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CHEMBL94277</t>
+          <t>CHEMBL202431</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -5428,7 +5428,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CHEMBL106708</t>
+          <t>CHEMBL202609</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -5444,7 +5444,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CHEMBL107316</t>
+          <t>CHEMBL202839</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -5460,7 +5460,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CHEMBL191275</t>
+          <t>CHEMBL207994</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -5476,7 +5476,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CHEMBL192894</t>
+          <t>CHEMBL208239</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -5492,23 +5492,23 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CHEMBL193233</t>
+          <t>CHEMBL2089125</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>1</v>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CHEMBL194176</t>
+          <t>CHEMBL209073</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -5524,23 +5524,23 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CHEMBL194805</t>
+          <t>CHEMBL203407</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>1</v>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CHEMBL194911</t>
+          <t>CHEMBL203517</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -5556,23 +5556,23 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CHEMBL204997</t>
+          <t>CHEMBL203631</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>1</v>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CHEMBL205437</t>
+          <t>CHEMBL203836</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -5588,7 +5588,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CHEMBL205786</t>
+          <t>CHEMBL204086</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -5604,7 +5604,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CHEMBL200255</t>
+          <t>CHEMBL204459</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -5620,23 +5620,23 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CHEMBL200469</t>
+          <t>CHEMBL189938</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CHEMBL200495</t>
+          <t>CHEMBL190201</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -5652,7 +5652,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CHEMBL201880</t>
+          <t>CHEMBL190801</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -5668,7 +5668,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CHEMBL202431</t>
+          <t>CHEMBL184444</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -5684,23 +5684,23 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CHEMBL202609</t>
+          <t>CHEMBL207496</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CHEMBL202839</t>
+          <t>CHEMBL207701</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -5716,7 +5716,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CHEMBL207994</t>
+          <t>CHEMBL207729</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -5732,7 +5732,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CHEMBL208239</t>
+          <t>CHEMBL185097</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -5748,23 +5748,23 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CHEMBL2089125</t>
+          <t>CHEMBL18591</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>1</v>
       </c>
       <c r="C136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CHEMBL209073</t>
+          <t>CHEMBL188865</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -5780,39 +5780,39 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CHEMBL203407</t>
+          <t>CHEMBL205821</t>
         </is>
       </c>
       <c r="B138" t="n">
         <v>1</v>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CHEMBL203517</t>
+          <t>CHEMBL207228</t>
         </is>
       </c>
       <c r="B139" t="n">
         <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CHEMBL203631</t>
+          <t>CHEMBL189434</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -5828,7 +5828,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CHEMBL203836</t>
+          <t>CHEMBL18136</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -5844,7 +5844,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CHEMBL204086</t>
+          <t>CHEMBL181936</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -5860,7 +5860,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CHEMBL204459</t>
+          <t>CHEMBL182323</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -5876,39 +5876,39 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CHEMBL189938</t>
+          <t>CHEMBL184151</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CHEMBL190201</t>
+          <t>CHEMBL209740</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>1</v>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CHEMBL190801</t>
+          <t>CHEMBL180300</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -5924,7 +5924,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CHEMBL184444</t>
+          <t>CHEMBL178090</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -5940,23 +5940,23 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CHEMBL207496</t>
+          <t>CHEMBL178130</t>
         </is>
       </c>
       <c r="B148" t="n">
         <v>1</v>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CHEMBL207701</t>
+          <t>CHEMBL178938</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -5972,7 +5972,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CHEMBL207729</t>
+          <t>CHEMBL217914</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -5988,7 +5988,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CHEMBL185097</t>
+          <t>CHEMBL218006</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -6004,7 +6004,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CHEMBL18591</t>
+          <t>CHEMBL174539</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -6020,7 +6020,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CHEMBL188865</t>
+          <t>CHEMBL175198</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -6036,7 +6036,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CHEMBL205821</t>
+          <t>CHEMBL169526</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -6052,23 +6052,23 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CHEMBL207228</t>
+          <t>CHEMBL213758</t>
         </is>
       </c>
       <c r="B155" t="n">
         <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CHEMBL189434</t>
+          <t>CHEMBL214502</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -6084,7 +6084,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CHEMBL18136</t>
+          <t>CHEMBL215344</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -6100,7 +6100,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CHEMBL181936</t>
+          <t>CHEMBL216697</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -6116,55 +6116,55 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CHEMBL182323</t>
+          <t>CHEMBL223339</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>1</v>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CHEMBL184151</t>
+          <t>CHEMBL223512</t>
         </is>
       </c>
       <c r="B160" t="n">
         <v>1</v>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CHEMBL209740</t>
+          <t>CHEMBL218289</t>
         </is>
       </c>
       <c r="B161" t="n">
         <v>1</v>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CHEMBL180300</t>
+          <t>CHEMBL218382</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -6180,7 +6180,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CHEMBL178090</t>
+          <t>CHEMBL219484</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -6196,23 +6196,23 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CHEMBL178130</t>
+          <t>CHEMBL220320</t>
         </is>
       </c>
       <c r="B164" t="n">
         <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CHEMBL178938</t>
+          <t>CHEMBL220467</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -6228,7 +6228,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CHEMBL217914</t>
+          <t>CHEMBL220513</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -6244,7 +6244,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CHEMBL218006</t>
+          <t>CHEMBL220529</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -6260,7 +6260,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHEMBL174539</t>
+          <t>CHEMBL212616</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -6276,7 +6276,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CHEMBL175198</t>
+          <t>CHEMBL221735</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -6292,7 +6292,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CHEMBL169526</t>
+          <t>CHEMBL223147</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -6308,7 +6308,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CHEMBL213758</t>
+          <t>CHEMBL223873</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -6324,7 +6324,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CHEMBL214502</t>
+          <t>CHEMBL225210</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -6340,7 +6340,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CHEMBL215344</t>
+          <t>CHEMBL225664</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -6356,23 +6356,23 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CHEMBL216697</t>
+          <t>CHEMBL226403</t>
         </is>
       </c>
       <c r="B174" t="n">
         <v>1</v>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CHEMBL223339</t>
+          <t>CHEMBL226471</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -6388,7 +6388,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CHEMBL223512</t>
+          <t>CHEMBL221181</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -6404,7 +6404,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CHEMBL218289</t>
+          <t>CHEMBL233360</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -6420,87 +6420,87 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CHEMBL218382</t>
+          <t>CHEMBL233553</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>1</v>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CHEMBL219484</t>
+          <t>CHEMBL233970</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>1</v>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CHEMBL220320</t>
+          <t>CHEMBL233992</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>1</v>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CHEMBL220467</t>
+          <t>CHEMBL227381</t>
         </is>
       </c>
       <c r="B181" t="n">
         <v>1</v>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CHEMBL220513</t>
+          <t>CHEMBL227924</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CHEMBL220529</t>
+          <t>CHEMBL227954</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -6516,39 +6516,39 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CHEMBL212616</t>
+          <t>CHEMBL228133</t>
         </is>
       </c>
       <c r="B184" t="n">
         <v>1</v>
       </c>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>METOCURINE IODIDE</t>
+          <t>CHEMBL228224</t>
         </is>
       </c>
       <c r="B185" t="n">
         <v>1</v>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CHEMBL221735</t>
+          <t>CHEMBL228369</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -6564,39 +6564,39 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CHEMBL223147</t>
+          <t>CHEMBL229855</t>
         </is>
       </c>
       <c r="B187" t="n">
         <v>1</v>
       </c>
       <c r="C187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CHEMBL223873</t>
+          <t>CHEMBL230153</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>1</v>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CHEMBL225210</t>
+          <t>CHEMBL230910</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -6612,55 +6612,55 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CHEMBL225664</t>
+          <t>CHEMBL165372</t>
         </is>
       </c>
       <c r="B190" t="n">
         <v>1</v>
       </c>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CHEMBL226403</t>
+          <t>FOLIC ACID</t>
         </is>
       </c>
       <c r="B191" t="n">
         <v>1</v>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D191" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CHEMBL226471</t>
+          <t>CHEMBL232566</t>
         </is>
       </c>
       <c r="B192" t="n">
         <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CHEMBL221181</t>
+          <t>CHEMBL232827</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -6676,7 +6676,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CHEMBL233360</t>
+          <t>CHEMBL232942</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -6692,7 +6692,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CHEMBL233553</t>
+          <t>CHEMBL233149</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -6708,103 +6708,103 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CHEMBL233970</t>
+          <t>CHEMBL233209</t>
         </is>
       </c>
       <c r="B196" t="n">
         <v>1</v>
       </c>
       <c r="C196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CHEMBL233992</t>
+          <t>CHEMBL233349</t>
         </is>
       </c>
       <c r="B197" t="n">
         <v>1</v>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CHEMBL227381</t>
+          <t>CHEMBL242737</t>
         </is>
       </c>
       <c r="B198" t="n">
         <v>1</v>
       </c>
       <c r="C198" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D198" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CHEMBL227924</t>
+          <t>CHEMBL243024</t>
         </is>
       </c>
       <c r="B199" t="n">
         <v>1</v>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D199" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CHEMBL227954</t>
+          <t>CHEMBL236086</t>
         </is>
       </c>
       <c r="B200" t="n">
         <v>1</v>
       </c>
       <c r="C200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>CHEMBL228133</t>
+          <t>CHEMBL236708</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>1</v>
       </c>
       <c r="C201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CHEMBL228224</t>
+          <t>CHEMBL236718</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -6820,7 +6820,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CHEMBL228369</t>
+          <t>CHEMBL237337</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -6836,39 +6836,39 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CHEMBL229855</t>
+          <t>CHEMBL237600</t>
         </is>
       </c>
       <c r="B204" t="n">
         <v>1</v>
       </c>
       <c r="C204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D204" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CHEMBL230153</t>
+          <t>CHEMBL237786</t>
         </is>
       </c>
       <c r="B205" t="n">
         <v>1</v>
       </c>
       <c r="C205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D205" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CHEMBL230910</t>
+          <t>CHEMBL239507</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -6884,7 +6884,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>CORTISONE ACETATE</t>
+          <t>CHEMBL239508</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -6900,39 +6900,39 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CHEMBL165372</t>
+          <t>CHEMBL240355</t>
         </is>
       </c>
       <c r="B208" t="n">
         <v>1</v>
       </c>
       <c r="C208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>FOLIC ACID</t>
+          <t>CHEMBL240719</t>
         </is>
       </c>
       <c r="B209" t="n">
         <v>1</v>
       </c>
       <c r="C209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>CHEMBL232566</t>
+          <t>CHEMBL240725</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -6948,7 +6948,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CHEMBL232827</t>
+          <t>CHEMBL241577</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -6964,7 +6964,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>CHEMBL232942</t>
+          <t>CHEMBL242237</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -6980,23 +6980,23 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CHEMBL233149</t>
+          <t>CHEMBL243731</t>
         </is>
       </c>
       <c r="B213" t="n">
         <v>1</v>
       </c>
       <c r="C213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D213" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CHEMBL233209</t>
+          <t>CHEMBL243940</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -7012,23 +7012,23 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CHEMBL233349</t>
+          <t>CHEMBL243978</t>
         </is>
       </c>
       <c r="B215" t="n">
         <v>1</v>
       </c>
       <c r="C215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CHEMBL242737</t>
+          <t>CHEMBL245678</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -7044,7 +7044,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CHEMBL243024</t>
+          <t>CHEMBL247272</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -7060,23 +7060,23 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CHEMBL236086</t>
+          <t>Phosphoric Acid Cyclohexylmethyl Ester 2-Formyl-Phenyl Ester</t>
         </is>
       </c>
       <c r="B218" t="n">
         <v>1</v>
       </c>
       <c r="C218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CHEMBL236708</t>
+          <t>CHEMBL248176</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -7092,23 +7092,23 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CHEMBL236718</t>
+          <t>CHEMBL248643</t>
         </is>
       </c>
       <c r="B220" t="n">
         <v>1</v>
       </c>
       <c r="C220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>CHEMBL237337</t>
+          <t>CHEMBL24957</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -7124,7 +7124,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CHEMBL237600</t>
+          <t>Mannitol Bis-Phosphate</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -7140,7 +7140,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CHEMBL237786</t>
+          <t>CHEMBL250409</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -7156,7 +7156,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CHEMBL239507</t>
+          <t>CHEMBL250787</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -7172,7 +7172,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CHEMBL239508</t>
+          <t>CHEMBL25186</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -7188,7 +7188,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CHEMBL240355</t>
+          <t>CHEMBL252967</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -7204,7 +7204,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CHEMBL240719</t>
+          <t>CHEMBL253608</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -7220,7 +7220,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CHEMBL240725</t>
+          <t>CHEMBL253825</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -7236,7 +7236,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CHEMBL241577</t>
+          <t>CHEMBL257543</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -7252,7 +7252,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CHEMBL242237</t>
+          <t>CHEMBL257626</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -7268,7 +7268,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CHEMBL243731</t>
+          <t>CHEMBL272114</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -7284,7 +7284,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>CHEMBL243940</t>
+          <t>CHEMBL272198</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -7300,7 +7300,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>CHEMBL243978</t>
+          <t>CHEMBL259420</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -7316,23 +7316,23 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CHEMBL245678</t>
+          <t>CHEMBL260000</t>
         </is>
       </c>
       <c r="B234" t="n">
         <v>1</v>
       </c>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>CHEMBL247272</t>
+          <t>CHEMBL262628</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -7348,23 +7348,23 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CHEMBL248176</t>
+          <t>CHEMBL254520</t>
         </is>
       </c>
       <c r="B236" t="n">
         <v>1</v>
       </c>
       <c r="C236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D236" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CHEMBL248643</t>
+          <t>CHEMBL159820</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -7380,23 +7380,23 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>CHEMBL24957</t>
+          <t>CHEMBL270672</t>
         </is>
       </c>
       <c r="B238" t="n">
         <v>1</v>
       </c>
       <c r="C238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D238" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Mannitol Bis-Phosphate</t>
+          <t>CHEMBL271138</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -7412,7 +7412,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>PARATOULENE PHOSPHATE</t>
+          <t>CHEMBL157105</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -7428,7 +7428,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Cytidine 3'-Phosphate</t>
+          <t>CHEMBL273822</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -7444,7 +7444,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CHEMBL250409</t>
+          <t>CHEMBL275339</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -7460,7 +7460,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CHEMBL250787</t>
+          <t>CHEMBL267048</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -7476,7 +7476,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CHEMBL25186</t>
+          <t>CHEMBL282837</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -7492,7 +7492,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CHEMBL252967</t>
+          <t>CHEMBL27784</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -7508,23 +7508,23 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>CHEMBL253608</t>
+          <t>RIBOFLAVIN</t>
         </is>
       </c>
       <c r="B246" t="n">
         <v>1</v>
       </c>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CHEMBL253825</t>
+          <t>CHEMBL149502</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -7540,7 +7540,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CHEMBL257543</t>
+          <t>CHEMBL149603</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -7556,7 +7556,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CHEMBL257626</t>
+          <t>CHEMBL1513348</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -7572,7 +7572,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>CHEMBL272114</t>
+          <t>CHEMBL281795</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -7588,7 +7588,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CHEMBL272198</t>
+          <t>CHEMBL282146</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -7604,39 +7604,39 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>CHEMBL259420</t>
+          <t>CHEMBL148333</t>
         </is>
       </c>
       <c r="B252" t="n">
         <v>1</v>
       </c>
       <c r="C252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D252" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>CHEMBL260000</t>
+          <t>Phosphoric Acid Benzyl Ester 2-Formyl-Phenyl Ester</t>
         </is>
       </c>
       <c r="B253" t="n">
         <v>1</v>
       </c>
       <c r="C253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D253" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PHENYL DIHYDROGEN PHOSPHATE</t>
+          <t>CHEMBL148732</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -7652,7 +7652,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CHEMBL262628</t>
+          <t>CHEMBL148756</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -7668,23 +7668,23 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CHEMBL254520</t>
+          <t>CHEMBL286364</t>
         </is>
       </c>
       <c r="B256" t="n">
         <v>1</v>
       </c>
       <c r="C256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D256" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CHEMBL159820</t>
+          <t>CHEMBL286678</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -7700,23 +7700,23 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CHEMBL270672</t>
+          <t>CHEMBL289422</t>
         </is>
       </c>
       <c r="B258" t="n">
         <v>1</v>
       </c>
       <c r="C258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D258" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CHEMBL271138</t>
+          <t>CHEMBL291678</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -7732,23 +7732,23 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CHOLINE ALFOSCERATE</t>
+          <t>CHEMBL292821</t>
         </is>
       </c>
       <c r="B260" t="n">
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D260" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>CHEMBL157105</t>
+          <t>CHEMBL293034</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -7764,23 +7764,23 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>CHEMBL273822</t>
+          <t>CHEMBL293212</t>
         </is>
       </c>
       <c r="B262" t="n">
         <v>1</v>
       </c>
       <c r="C262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D262" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>CHEMBL275339</t>
+          <t>CHEMBL142996</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -7796,7 +7796,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>CHEMBL267048</t>
+          <t>CHEMBL296323</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -7812,23 +7812,23 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CHEMBL282837</t>
+          <t>CHEMBL298445</t>
         </is>
       </c>
       <c r="B265" t="n">
         <v>1</v>
       </c>
       <c r="C265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D265" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CHEMBL27784</t>
+          <t>CHEMBL302715</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -7844,7 +7844,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>RIBOFLAVIN</t>
+          <t>CHEMBL303992</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -7860,7 +7860,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CHEMBL149502</t>
+          <t>CHEMBL304552</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -7876,7 +7876,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>CHEMBL149603</t>
+          <t>CHEMBL305785</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -7892,23 +7892,23 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CHEMBL1513348</t>
+          <t>CHEMBL306380</t>
         </is>
       </c>
       <c r="B270" t="n">
         <v>1</v>
       </c>
       <c r="C270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D270" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>GUANIDINO ACETATE</t>
+          <t>CHEMBL295971</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -7924,7 +7924,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CHEMBL281795</t>
+          <t>CHEMBL141889</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -7940,7 +7940,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CHEMBL282146</t>
+          <t>CHEMBL309282</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -7956,39 +7956,39 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>CHEMBL148333</t>
+          <t>CHEMBL310554</t>
         </is>
       </c>
       <c r="B274" t="n">
         <v>1</v>
       </c>
       <c r="C274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D274" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CHEMBL148732</t>
+          <t>CHEMBL311228</t>
         </is>
       </c>
       <c r="B275" t="n">
         <v>1</v>
       </c>
       <c r="C275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D275" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>CHEMBL148756</t>
+          <t>CHEMBL316053</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -8004,7 +8004,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>CHEMBL286364</t>
+          <t>CHEMBL316388</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -8020,7 +8020,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>CHEMBL286678</t>
+          <t>CHEMBL3185126</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -8036,55 +8036,55 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>CHEMBL289422</t>
+          <t>CHEMBL3185133</t>
         </is>
       </c>
       <c r="B279" t="n">
         <v>1</v>
       </c>
       <c r="C279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D279" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>CHEMBL291678</t>
+          <t>CHEMBL3186422</t>
         </is>
       </c>
       <c r="B280" t="n">
         <v>1</v>
       </c>
       <c r="C280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D280" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>CHEMBL292821</t>
+          <t>CHEMBL318721</t>
         </is>
       </c>
       <c r="B281" t="n">
         <v>1</v>
       </c>
       <c r="C281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D281" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>CHEMBL293034</t>
+          <t>CHEMBL329433</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -8100,23 +8100,23 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>CHEMBL293212</t>
+          <t>CHEMBL329985</t>
         </is>
       </c>
       <c r="B283" t="n">
         <v>1</v>
       </c>
       <c r="C283" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D283" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CHEMBL142996</t>
+          <t>CHEMBL319516</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -8132,7 +8132,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CHEMBL296323</t>
+          <t>CHEMBL321130</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -8148,39 +8148,39 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CHEMBL298445</t>
+          <t>CHEMBL321944</t>
         </is>
       </c>
       <c r="B286" t="n">
         <v>1</v>
       </c>
       <c r="C286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D286" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>CHEMBL302715</t>
+          <t>CHEMBL323556</t>
         </is>
       </c>
       <c r="B287" t="n">
         <v>1</v>
       </c>
       <c r="C287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>CHEMBL303992</t>
+          <t>CHEMBL323668</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -8196,7 +8196,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>CHEMBL304552</t>
+          <t>CHEMBL324168</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -8212,7 +8212,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>CHEMBL305785</t>
+          <t>CHEMBL138806</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -8228,23 +8228,23 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>CHEMBL306380</t>
+          <t>CHEMBL139393</t>
         </is>
       </c>
       <c r="B291" t="n">
         <v>1</v>
       </c>
       <c r="C291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D291" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>CHEMBL295971</t>
+          <t>CHEMBL139423</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -8260,7 +8260,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>CHEMBL141889</t>
+          <t>CHEMBL326082</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -8276,23 +8276,23 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Cytidine 5'-Phosphate</t>
+          <t>CHEMBL326523</t>
         </is>
       </c>
       <c r="B294" t="n">
         <v>1</v>
       </c>
       <c r="C294" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D294" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>CHEMBL309282</t>
+          <t>CHEMBL326564</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -8308,7 +8308,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>CHEMBL310554</t>
+          <t>CHEMBL326651</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -8324,23 +8324,23 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>CHEMBL311228</t>
+          <t>CHEMBL328139</t>
         </is>
       </c>
       <c r="B297" t="n">
         <v>1</v>
       </c>
       <c r="C297" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D297" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>CHEMBL316053</t>
+          <t>CHEMBL328827</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -8356,7 +8356,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>CHEMBL316388</t>
+          <t>CHEMBL331282</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -8372,7 +8372,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CHEMBL3185126</t>
+          <t>CHEMBL332935</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -8388,39 +8388,39 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>CHEMBL3185133</t>
+          <t>CHEMBL334167</t>
         </is>
       </c>
       <c r="B301" t="n">
         <v>1</v>
       </c>
       <c r="C301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D301" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>CHEMBL3186422</t>
+          <t>CHEMBL324951</t>
         </is>
       </c>
       <c r="B302" t="n">
         <v>1</v>
       </c>
       <c r="C302" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D302" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>CHEMBL318721</t>
+          <t>CHEMBL325029</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -8436,7 +8436,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>CHEMBL329433</t>
+          <t>CHEMBL336908</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -8452,7 +8452,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>CHEMBL329985</t>
+          <t>CHEMBL338076</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -8468,23 +8468,23 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>CHEMBL319516</t>
+          <t>CHEMBL339611</t>
         </is>
       </c>
       <c r="B306" t="n">
         <v>1</v>
       </c>
       <c r="C306" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D306" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CHEMBL321130</t>
+          <t>CHEMBL34062</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -8500,55 +8500,55 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>CHEMBL321944</t>
+          <t>CHEMBL341273</t>
         </is>
       </c>
       <c r="B308" t="n">
         <v>1</v>
       </c>
       <c r="C308" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>CHEMBL323556</t>
+          <t>CHEMBL342478</t>
         </is>
       </c>
       <c r="B309" t="n">
         <v>1</v>
       </c>
       <c r="C309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D309" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CHEMBL323668</t>
+          <t>CHEMBL343336</t>
         </is>
       </c>
       <c r="B310" t="n">
         <v>1</v>
       </c>
       <c r="C310" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D310" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>CHEMBL324168</t>
+          <t>CHEMBL135287</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -8564,23 +8564,23 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>CHEMBL138806</t>
+          <t>CHEMBL1313657</t>
         </is>
       </c>
       <c r="B312" t="n">
         <v>1</v>
       </c>
       <c r="C312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>CHEMBL139393</t>
+          <t>CHEMBL35107</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -8596,7 +8596,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>CHEMBL139423</t>
+          <t>CHEMBL351298</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -8612,23 +8612,23 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>CYPROTERONE ACETATE</t>
+          <t>CHEMBL363847</t>
         </is>
       </c>
       <c r="B315" t="n">
         <v>1</v>
       </c>
       <c r="C315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D315" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>CHEMBL326082</t>
+          <t>CHEMBL364748</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -8644,7 +8644,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CHEMBL326523</t>
+          <t>CHEMBL355497</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -8660,23 +8660,23 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>CHEMBL326564</t>
+          <t>CHEMBL3559901</t>
         </is>
       </c>
       <c r="B318" t="n">
         <v>1</v>
       </c>
       <c r="C318" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>CHEMBL326651</t>
+          <t>CHEMBL356002</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -8692,7 +8692,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>CHEMBL328139</t>
+          <t>CHEMBL356752</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -8708,7 +8708,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>CHEMBL328827</t>
+          <t>CHEMBL357488</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -8724,7 +8724,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>CHEMBL331282</t>
+          <t>CHEMBL359482</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -8740,7 +8740,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>CHEMBL332935</t>
+          <t>CHEMBL360356</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -8756,23 +8756,23 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CHEMBL334167</t>
+          <t>CHEMBL360520</t>
         </is>
       </c>
       <c r="B324" t="n">
         <v>1</v>
       </c>
       <c r="C324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D324" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>CHEMBL324951</t>
+          <t>CHEMBL360563</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -8788,7 +8788,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>CHEMBL325029</t>
+          <t>CHEMBL360998</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -8804,7 +8804,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>CHEMBL336908</t>
+          <t>CHEMBL361078</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -8820,7 +8820,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>CHEMBL338076</t>
+          <t>CHEMBL363302</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -8836,7 +8836,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>CHEMBL339611</t>
+          <t>CHEMBL376388</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -8852,7 +8852,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>CHEMBL34062</t>
+          <t>CHEMBL364811</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -8868,23 +8868,23 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>CHEMBL341273</t>
+          <t>CHEMBL366312</t>
         </is>
       </c>
       <c r="B331" t="n">
         <v>1</v>
       </c>
       <c r="C331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D331" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>CHEMBL342478</t>
+          <t>CHEMBL368238</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -8900,7 +8900,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CHEMBL343336</t>
+          <t>CHEMBL358860</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -8916,7 +8916,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>CHEMBL135287</t>
+          <t>CHEMBL358866</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -8932,23 +8932,23 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>CHEMBL1313657</t>
+          <t>CHEMBL379692</t>
         </is>
       </c>
       <c r="B335" t="n">
         <v>1</v>
       </c>
       <c r="C335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D335" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>CHEMBL35107</t>
+          <t>CHEMBL380589</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -8964,7 +8964,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>CHEMBL351298</t>
+          <t>CHEMBL380888</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -8980,7 +8980,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>CHEMBL363847</t>
+          <t>CHEMBL380955</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -8996,7 +8996,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>CHEMBL364748</t>
+          <t>CHEMBL371732</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -9012,39 +9012,39 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>CHEMBL355497</t>
+          <t>CHEMBL372164</t>
         </is>
       </c>
       <c r="B340" t="n">
         <v>1</v>
       </c>
       <c r="C340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D340" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>CHEMBL3559901</t>
+          <t>CHEMBL373357</t>
         </is>
       </c>
       <c r="B341" t="n">
         <v>1</v>
       </c>
       <c r="C341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D341" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>CHEMBL356002</t>
+          <t>CHEMBL374713</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -9060,7 +9060,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>CHEMBL356752</t>
+          <t>CHEMBL374936</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -9076,7 +9076,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>CHEMBL357488</t>
+          <t>CHEMBL375112</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -9092,7 +9092,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>CHEMBL359482</t>
+          <t>CHEMBL126589</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -9108,39 +9108,39 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>CHEMBL360356</t>
+          <t>CHEMBL377956</t>
         </is>
       </c>
       <c r="B346" t="n">
         <v>1</v>
       </c>
       <c r="C346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>CHEMBL360520</t>
+          <t>CHEMBL378160</t>
         </is>
       </c>
       <c r="B347" t="n">
         <v>1</v>
       </c>
       <c r="C347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D347" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>CHEMBL360563</t>
+          <t>CHEMBL385711</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -9156,7 +9156,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>CHEMBL360998</t>
+          <t>CHEMBL385937</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -9172,7 +9172,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>CHEMBL361078</t>
+          <t>CHEMBL381806</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -9188,7 +9188,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CHEMBL363302</t>
+          <t>CHEMBL382311</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -9204,7 +9204,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>CHEMBL376388</t>
+          <t>CHEMBL382639</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -9220,7 +9220,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>CHEMBL364811</t>
+          <t>ALUMINUM CHLORIDE</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -9236,23 +9236,23 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>CHEMBL366312</t>
+          <t>CHEMBL383541</t>
         </is>
       </c>
       <c r="B354" t="n">
         <v>1</v>
       </c>
       <c r="C354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>CHEMBL368238</t>
+          <t>CHEMBL383570</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -9268,7 +9268,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>CHEMBL358860</t>
+          <t>CHEMBL383705</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -9284,7 +9284,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>CHEMBL358866</t>
+          <t>CHEMBL376632</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -9300,7 +9300,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>CHEMBL379692</t>
+          <t>CHEMBL377312</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -9316,7 +9316,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>CHEMBL380589</t>
+          <t>CHEMBL124493</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -9332,7 +9332,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>CHEMBL380888</t>
+          <t>CHEMBL124718</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -9348,7 +9348,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>CHEMBL380955</t>
+          <t>CHEMBL125236</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -9364,7 +9364,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>CHEMBL371732</t>
+          <t>CHEMBL125381</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -9380,23 +9380,23 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>CHEMBL372164</t>
+          <t>CHEMBL125386</t>
         </is>
       </c>
       <c r="B363" t="n">
         <v>1</v>
       </c>
       <c r="C363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D363" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>CHEMBL373357</t>
+          <t>CHEMBL383990</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -9412,7 +9412,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CHEMBL374713</t>
+          <t>CHEMBL385178</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -9428,7 +9428,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>CHEMBL374936</t>
+          <t>CHEMBL385587</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -9444,7 +9444,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>CHEMBL375112</t>
+          <t>CHEMBL398346</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -9460,7 +9460,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>CHEMBL126589</t>
+          <t>CHEMBL390674</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -9476,23 +9476,23 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>CHEMBL377956</t>
+          <t>CHEMBL391805</t>
         </is>
       </c>
       <c r="B369" t="n">
         <v>1</v>
       </c>
       <c r="C369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D369" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>CHEMBL378160</t>
+          <t>CHEMBL391910</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -9508,7 +9508,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>CHEMBL385711</t>
+          <t>CHEMBL3924132</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -9524,7 +9524,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>CHEMBL385937</t>
+          <t>CHEMBL392452</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -9540,7 +9540,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>CHEMBL381806</t>
+          <t>CHEMBL392990</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -9556,7 +9556,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>CHEMBL382311</t>
+          <t>CHEMBL383921</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -9572,23 +9572,23 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>CHEMBL382639</t>
+          <t>CHEMBL398940</t>
         </is>
       </c>
       <c r="B375" t="n">
         <v>1</v>
       </c>
       <c r="C375" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D375" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>ALUMINUM CHLORIDE</t>
+          <t>CHEMBL399598</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -9604,23 +9604,23 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>CHEMBL383541</t>
+          <t>CHEMBL400431</t>
         </is>
       </c>
       <c r="B377" t="n">
         <v>1</v>
       </c>
       <c r="C377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D377" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>CHEMBL383570</t>
+          <t>CHEMBL400841</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -9636,7 +9636,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>CHEMBL383705</t>
+          <t>CHEMBL393949</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -9652,7 +9652,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>CHEMBL376632</t>
+          <t>CHEMBL394484</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -9668,7 +9668,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>CHEMBL377312</t>
+          <t>CHEMBL3945401</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -9684,7 +9684,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>CHEMBL124493</t>
+          <t>CHEMBL394826</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -9700,7 +9700,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>CHEMBL124718</t>
+          <t>CHEMBL395280</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -9716,7 +9716,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>CHEMBL125236</t>
+          <t>CHEMBL395347</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -9732,7 +9732,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>CHEMBL125381</t>
+          <t>CHEMBL396380</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -9748,7 +9748,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>CHEMBL125386</t>
+          <t>CHEMBL398428</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -9764,7 +9764,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>CHEMBL383990</t>
+          <t>CHEMBL1235806</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -9780,7 +9780,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>CHEMBL385178</t>
+          <t>CHEMBL1236157</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -9796,7 +9796,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>CHEMBL385587</t>
+          <t>CHEMBL1236215</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -9812,7 +9812,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>CHEMBL398346</t>
+          <t>CHEMBL1236268</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -9828,7 +9828,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>CHEMBL390674</t>
+          <t>CHEMBL1236302</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -9844,23 +9844,23 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>CHEMBL391805</t>
+          <t>CHEMBL1236433</t>
         </is>
       </c>
       <c r="B392" t="n">
         <v>1</v>
       </c>
       <c r="C392" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D392" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>CHEMBL391910</t>
+          <t>CHEMBL408967</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -9876,23 +9876,23 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>CHEMBL3924132</t>
+          <t>CHEMBL41036</t>
         </is>
       </c>
       <c r="B394" t="n">
         <v>1</v>
       </c>
       <c r="C394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D394" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>CHEMBL392452</t>
+          <t>CHEMBL401150</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -9908,7 +9908,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>CHEMBL392990</t>
+          <t>CHEMBL401365</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -9924,7 +9924,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>CHEMBL383921</t>
+          <t>CHEMBL401842</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -9940,7 +9940,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>CHEMBL398940</t>
+          <t>CHEMBL402262</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -9956,7 +9956,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>CHEMBL399598</t>
+          <t>CHEMBL402747</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -9972,7 +9972,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>CHEMBL400431</t>
+          <t>CHEMBL402761</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -9988,7 +9988,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>CHEMBL400841</t>
+          <t>CHEMBL404630</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -10004,23 +10004,23 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>CHEMBL393949</t>
+          <t>PYRIDOXAMINE PHOSPHATE ANHYDROUS</t>
         </is>
       </c>
       <c r="B402" t="n">
         <v>1</v>
       </c>
       <c r="C402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D402" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>CHEMBL394484</t>
+          <t>CHEMBL1235380</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -10036,7 +10036,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>CHEMBL3945401</t>
+          <t>CHEMBL1235423</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -10052,7 +10052,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>CHEMBL394826</t>
+          <t>CHEMBL1235556</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -10068,7 +10068,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>CHEMBL395280</t>
+          <t>CHEMBL1235676</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -10084,7 +10084,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CHEMBL395347</t>
+          <t>CHEMBL1235693</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -10100,7 +10100,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>CHEMBL396380</t>
+          <t>CHEMBL1235702</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -10116,23 +10116,23 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>CHEMBL398428</t>
+          <t>CHEMBL1234624</t>
         </is>
       </c>
       <c r="B409" t="n">
         <v>1</v>
       </c>
       <c r="C409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D409" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>CHEMBL1235806</t>
+          <t>CHEMBL406572</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -10148,23 +10148,23 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>CHEMBL1236157</t>
+          <t>CHEMBL406863</t>
         </is>
       </c>
       <c r="B411" t="n">
         <v>1</v>
       </c>
       <c r="C411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D411" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>CHEMBL1236215</t>
+          <t>CHEMBL42039</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -10180,23 +10180,23 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CHEMBL1236268</t>
+          <t>CHEMBL420671</t>
         </is>
       </c>
       <c r="B413" t="n">
         <v>1</v>
       </c>
       <c r="C413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D413" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>CHEMBL1236302</t>
+          <t>CHEMBL421138</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -10212,23 +10212,23 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>CHEMBL1236433</t>
+          <t>CHEMBL410448</t>
         </is>
       </c>
       <c r="B415" t="n">
         <v>1</v>
       </c>
       <c r="C415" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D415" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>CHEMBL408967</t>
+          <t>CHEMBL410462</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -10244,23 +10244,23 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>CHEMBL41036</t>
+          <t>CHEMBL411930</t>
         </is>
       </c>
       <c r="B417" t="n">
         <v>1</v>
       </c>
       <c r="C417" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D417" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>CHEMBL401150</t>
+          <t>CHEMBL417656</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -10276,7 +10276,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CHEMBL401365</t>
+          <t>CHEMBL417844</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -10292,7 +10292,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CHEMBL401842</t>
+          <t>CHEMBL1234777</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -10308,7 +10308,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CHEMBL402262</t>
+          <t>CHEMBL1234797</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -10324,7 +10324,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>CHEMBL402747</t>
+          <t>CHEMBL1234815</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -10340,7 +10340,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>CHEMBL402761</t>
+          <t>CHEMBL1234916</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -10356,7 +10356,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>CHEMBL404630</t>
+          <t>CHEMBL1235084</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -10372,23 +10372,23 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>PYRIDOXAMINE PHOSPHATE ANHYDROUS</t>
+          <t>CHEMBL1235106</t>
         </is>
       </c>
       <c r="B425" t="n">
         <v>1</v>
       </c>
       <c r="C425" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D425" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>CHEMBL1235380</t>
+          <t>CHEMBL1235110</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -10404,7 +10404,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>CHEMBL1235423</t>
+          <t>CHEMBL1235136</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -10420,7 +10420,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>CHEMBL1235556</t>
+          <t>CHEMBL1235151</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -10436,7 +10436,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>CHEMBL1235676</t>
+          <t>CHEMBL420311</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -10452,7 +10452,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>CHEMBL1235693</t>
+          <t>CHEMBL425584</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -10468,7 +10468,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>CHEMBL1235702</t>
+          <t>CHEMBL425646</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -10484,23 +10484,23 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>CHEMBL1234624</t>
+          <t>CHEMBL426815</t>
         </is>
       </c>
       <c r="B432" t="n">
         <v>1</v>
       </c>
       <c r="C432" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D432" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>CHEMBL406572</t>
+          <t>CHEMBL427896</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -10516,71 +10516,71 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CHEMBL406863</t>
+          <t>CHEMBL4280145</t>
         </is>
       </c>
       <c r="B434" t="n">
         <v>1</v>
       </c>
       <c r="C434" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D434" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CHEMBL42039</t>
+          <t>CHEMBL428462</t>
         </is>
       </c>
       <c r="B435" t="n">
         <v>1</v>
       </c>
       <c r="C435" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D435" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CHEMBL420671</t>
+          <t>CHEMBL1234640</t>
         </is>
       </c>
       <c r="B436" t="n">
         <v>1</v>
       </c>
       <c r="C436" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D436" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>CHEMBL421138</t>
+          <t>CHEMBL1234669</t>
         </is>
       </c>
       <c r="B437" t="n">
         <v>1</v>
       </c>
       <c r="C437" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D437" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CHEMBL410448</t>
+          <t>CHEMBL432359</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -10596,71 +10596,71 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>CHEMBL410462</t>
+          <t>CHEMBL433501</t>
         </is>
       </c>
       <c r="B439" t="n">
         <v>1</v>
       </c>
       <c r="C439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D439" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>CHEMBL411930</t>
+          <t>CHEMBL439009</t>
         </is>
       </c>
       <c r="B440" t="n">
         <v>1</v>
       </c>
       <c r="C440" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D440" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>CHEMBL417656</t>
+          <t>CHEMBL1234032</t>
         </is>
       </c>
       <c r="B441" t="n">
         <v>1</v>
       </c>
       <c r="C441" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D441" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>CHEMBL417844</t>
+          <t>CHEMBL1234033</t>
         </is>
       </c>
       <c r="B442" t="n">
         <v>1</v>
       </c>
       <c r="C442" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D442" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>CHEMBL1234777</t>
+          <t>CHEMBL1234048</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -10676,7 +10676,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>CHEMBL1234797</t>
+          <t>CHEMBL1234135</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -10692,7 +10692,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>CHEMBL1234815</t>
+          <t>CHEMBL1234162</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -10708,7 +10708,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CHEMBL1234916</t>
+          <t>CHEMBL1234200</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -10724,7 +10724,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>CHEMBL1235084</t>
+          <t>CHEMBL123440</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -10740,7 +10740,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>CHEMBL1235106</t>
+          <t>CHEMBL1234416</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -10756,7 +10756,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>CHEMBL1235110</t>
+          <t>CHEMBL1234585</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -10772,7 +10772,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>CHEMBL1235136</t>
+          <t>CHEMBL430879</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -10788,7 +10788,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>CHEMBL1235151</t>
+          <t>CHEMBL436462</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -10804,23 +10804,23 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>CHEMBL420311</t>
+          <t>CHEMBL437508</t>
         </is>
       </c>
       <c r="B452" t="n">
         <v>1</v>
       </c>
       <c r="C452" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D452" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>CHEMBL425584</t>
+          <t>CHEMBL437557</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -10836,7 +10836,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>CHEMBL425646</t>
+          <t>CHEMBL437747</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -10852,23 +10852,23 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>CHEMBL426815</t>
+          <t>CHEMBL123368</t>
         </is>
       </c>
       <c r="B455" t="n">
         <v>1</v>
       </c>
       <c r="C455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D455" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>CHEMBL427896</t>
+          <t>CHEMBL1233749</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -10884,7 +10884,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>CHEMBL4280145</t>
+          <t>CHEMBL1233797</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -10900,23 +10900,23 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>CHEMBL428462</t>
+          <t>CHEMBL1233881</t>
         </is>
       </c>
       <c r="B458" t="n">
         <v>1</v>
       </c>
       <c r="C458" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D458" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>CHEMBL1234640</t>
+          <t>CHEMBL1233882</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -10932,23 +10932,23 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>CHEMBL1234669</t>
+          <t>CHEMBL1233960</t>
         </is>
       </c>
       <c r="B460" t="n">
         <v>1</v>
       </c>
       <c r="C460" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D460" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>CHEMBL432359</t>
+          <t>CHEMBL1231778</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -10964,71 +10964,71 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>CHEMBL433501</t>
+          <t>CHEMBL1231797</t>
         </is>
       </c>
       <c r="B462" t="n">
         <v>1</v>
       </c>
       <c r="C462" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D462" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>CHEMBL439009</t>
+          <t>CHEMBL452289</t>
         </is>
       </c>
       <c r="B463" t="n">
         <v>1</v>
       </c>
       <c r="C463" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D463" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>CHEMBL1234032</t>
+          <t>CHEMBL452587</t>
         </is>
       </c>
       <c r="B464" t="n">
         <v>1</v>
       </c>
       <c r="C464" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D464" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CHEMBL1234033</t>
+          <t>CHEMBL453620</t>
         </is>
       </c>
       <c r="B465" t="n">
         <v>1</v>
       </c>
       <c r="C465" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D465" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>CHEMBL1234048</t>
+          <t>CHEMBL455271</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -11044,7 +11044,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>CHEMBL1234135</t>
+          <t>CHEMBL455333</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -11060,7 +11060,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>CHEMBL1234162</t>
+          <t>CHEMBL446435</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -11076,23 +11076,23 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>CHEMBL1234200</t>
+          <t>CHEMBL451509</t>
         </is>
       </c>
       <c r="B469" t="n">
         <v>1</v>
       </c>
       <c r="C469" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D469" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>CHEMBL123440</t>
+          <t>Selenazole-4-Carboxamide Adenine Dinucleotide</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -11108,7 +11108,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>CHEMBL1234416</t>
+          <t>CHEMBL1231909</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -11124,39 +11124,39 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>CHEMBL1234585</t>
+          <t>CHEMBL1232157</t>
         </is>
       </c>
       <c r="B472" t="n">
         <v>1</v>
       </c>
       <c r="C472" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D472" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CHEMBL430879</t>
+          <t>CHEMBL1232243</t>
         </is>
       </c>
       <c r="B473" t="n">
         <v>1</v>
       </c>
       <c r="C473" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D473" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>BERAPROST SODIUM</t>
+          <t>CHEMBL1232261</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -11172,7 +11172,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>CHEMBL436462</t>
+          <t>CHEMBL1232391</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -11188,23 +11188,23 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>CHEMBL437508</t>
+          <t>CHEMBL1232829</t>
         </is>
       </c>
       <c r="B476" t="n">
         <v>1</v>
       </c>
       <c r="C476" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D476" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>CHEMBL437557</t>
+          <t>CHEMBL1230661</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -11220,7 +11220,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>CHEMBL437747</t>
+          <t>CHEMBL1230662</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -11236,23 +11236,23 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>CHEMBL123368</t>
+          <t>CHEMBL462228</t>
         </is>
       </c>
       <c r="B479" t="n">
         <v>1</v>
       </c>
       <c r="C479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D479" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>CHEMBL1233749</t>
+          <t>CHEMBL462712</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -11268,7 +11268,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>CHEMBL1233797</t>
+          <t>CHEMBL455907</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -11284,23 +11284,23 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>CHEMBL1233881</t>
+          <t>CHEMBL457530</t>
         </is>
       </c>
       <c r="B482" t="n">
         <v>1</v>
       </c>
       <c r="C482" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D482" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>CHEMBL1233882</t>
+          <t>CHEMBL458975</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -11316,7 +11316,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>CHEMBL1233960</t>
+          <t>CHEMBL459149</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -11332,7 +11332,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>CHEMBL1231778</t>
+          <t>CHEMBL46780</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -11348,23 +11348,23 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>CHEMBL1231797</t>
+          <t>CHEMBL46817</t>
         </is>
       </c>
       <c r="B486" t="n">
         <v>1</v>
       </c>
       <c r="C486" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D486" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>CHEMBL452289</t>
+          <t>CHEMBL469099</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -11380,7 +11380,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>CHEMBL452587</t>
+          <t>CHEMBL470365</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -11396,7 +11396,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>CHEMBL453620</t>
+          <t>CHEMBL460910</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -11412,7 +11412,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>CHEMBL455271</t>
+          <t>CHEMBL460962</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -11428,23 +11428,23 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>CHEMBL455333</t>
+          <t>CHEMBL46148</t>
         </is>
       </c>
       <c r="B491" t="n">
         <v>1</v>
       </c>
       <c r="C491" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D491" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>CHEMBL446435</t>
+          <t>CHEMBL1230763</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -11460,23 +11460,23 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>CHEMBL451509</t>
+          <t>CHEMBL1230893</t>
         </is>
       </c>
       <c r="B493" t="n">
         <v>1</v>
       </c>
       <c r="C493" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D493" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Selenazole-4-Carboxamide Adenine Dinucleotide</t>
+          <t>CHEMBL1231193</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -11492,7 +11492,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>CHEMBL1231909</t>
+          <t>CHEMBL1231206</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -11508,39 +11508,39 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>CHEMBL1232157</t>
+          <t>CHEMBL1231453</t>
         </is>
       </c>
       <c r="B496" t="n">
         <v>1</v>
       </c>
       <c r="C496" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D496" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>CHEMBL1232243</t>
+          <t>CHEMBL1231533</t>
         </is>
       </c>
       <c r="B497" t="n">
         <v>1</v>
       </c>
       <c r="C497" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D497" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>CHEMBL1232261</t>
+          <t>CHEMBL1231592</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -11556,7 +11556,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>CHEMBL1232391</t>
+          <t>CHEMBL1231666</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -11572,7 +11572,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>D-Erythrose 4-Phosphate</t>
+          <t>CHEMBL1229677</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -11588,7 +11588,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>CHEMBL1232829</t>
+          <t>CHEMBL1229801</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -11604,7 +11604,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>CHEMBL1230661</t>
+          <t>CHEMBL472193</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -11620,23 +11620,23 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>CHEMBL1230662</t>
+          <t>CHEMBL47302</t>
         </is>
       </c>
       <c r="B503" t="n">
         <v>1</v>
       </c>
       <c r="C503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D503" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>CHEMBL462228</t>
+          <t>CHEMBL473922</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -11652,7 +11652,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>CHEMBL462712</t>
+          <t>CHEMBL475814</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -11668,7 +11668,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>CHEMBL455907</t>
+          <t>CHEMBL466496</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -11684,23 +11684,23 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>CHEMBL457530</t>
+          <t>CHEMBL1230670</t>
         </is>
       </c>
       <c r="B507" t="n">
         <v>1</v>
       </c>
       <c r="C507" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D507" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>CHEMBL458975</t>
+          <t>CHEMBL486921</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -11716,7 +11716,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>CHEMBL459149</t>
+          <t>CHEMBL478464</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -11732,23 +11732,23 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>CHEMBL46780</t>
+          <t>CHEMBL479014</t>
         </is>
       </c>
       <c r="B510" t="n">
         <v>1</v>
       </c>
       <c r="C510" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D510" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>CHEMBL46817</t>
+          <t>CHEMBL48109</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -11764,23 +11764,23 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>CHEMBL469099</t>
+          <t>CHEMBL482193</t>
         </is>
       </c>
       <c r="B512" t="n">
         <v>1</v>
       </c>
       <c r="C512" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D512" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>CHEMBL470365</t>
+          <t>CHEMBL482708</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -11796,7 +11796,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Uridine 3'-Phosphate</t>
+          <t>CHEMBL1230044</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -11812,7 +11812,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Arabinouridine 3'-Phosphate</t>
+          <t>CHEMBL1230062</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -11828,7 +11828,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>CHEMBL460910</t>
+          <t>CHEMBL1230270</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -11844,7 +11844,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>CHEMBL460962</t>
+          <t>CHEMBL1230612</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -11860,7 +11860,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>ROXATIDINE ACETATE</t>
+          <t>CHEMBL1230658</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -11876,23 +11876,23 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>CHEMBL46148</t>
+          <t>CHEMBL121790</t>
         </is>
       </c>
       <c r="B519" t="n">
         <v>1</v>
       </c>
       <c r="C519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D519" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>CHEMBL1230763</t>
+          <t>CHEMBL483716</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -11908,7 +11908,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>CHEMBL1230893</t>
+          <t>CHEMBL483849</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -11924,7 +11924,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>CHEMBL1231193</t>
+          <t>CHEMBL483995</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -11940,7 +11940,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>CHEMBL1231206</t>
+          <t>CHEMBL484726</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -11956,7 +11956,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>CHEMBL1231453</t>
+          <t>CHEMBL484780</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -11972,7 +11972,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>CHEMBL1231533</t>
+          <t>CHEMBL485323</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -11988,7 +11988,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>CHEMBL1231592</t>
+          <t>CHEMBL485835</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -12004,7 +12004,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>CHEMBL1231666</t>
+          <t>CHEMBL485945</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -12020,7 +12020,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>CHEMBL1229677</t>
+          <t>CHEMBL487431</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -12036,7 +12036,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>CHEMBL1229801</t>
+          <t>CHEMBL48813</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -12052,7 +12052,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>CHEMBL472193</t>
+          <t>CHEMBL490730</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -12068,23 +12068,23 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>CHEMBL47302</t>
+          <t>CHEMBL490814</t>
         </is>
       </c>
       <c r="B531" t="n">
         <v>1</v>
       </c>
       <c r="C531" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D531" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>CHEMBL473922</t>
+          <t>CHEMBL490866</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -12100,7 +12100,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>CHEMBL475814</t>
+          <t>CHEMBL491429</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -12116,7 +12116,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>CHEMBL466496</t>
+          <t>CHEMBL483161</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -12132,7 +12132,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>CHEMBL1230670</t>
+          <t>CHEMBL1229851</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -12148,7 +12148,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>CHEMBL486921</t>
+          <t>CHEMBL1229855</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -12164,7 +12164,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>CHEMBL478464</t>
+          <t>CHEMBL1229914</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -12180,55 +12180,55 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>CHEMBL479014</t>
+          <t>CHEMBL1229989</t>
         </is>
       </c>
       <c r="B538" t="n">
         <v>1</v>
       </c>
       <c r="C538" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D538" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>CHEMBL48109</t>
+          <t>CHEMBL1230016</t>
         </is>
       </c>
       <c r="B539" t="n">
         <v>1</v>
       </c>
       <c r="C539" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D539" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>CHEMBL482193</t>
+          <t>CHEMBL506972</t>
         </is>
       </c>
       <c r="B540" t="n">
         <v>1</v>
       </c>
       <c r="C540" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D540" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>CHEMBL482708</t>
+          <t>CHEMBL509101</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -12244,7 +12244,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>CHEMBL1230044</t>
+          <t>CHEMBL493986</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -12260,7 +12260,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>CHEMBL1230062</t>
+          <t>CHEMBL495597</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -12276,7 +12276,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>CHEMBL1230270</t>
+          <t>CHEMBL495758</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -12292,23 +12292,23 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>CHEMBL1230612</t>
+          <t>CHEMBL496879</t>
         </is>
       </c>
       <c r="B545" t="n">
         <v>1</v>
       </c>
       <c r="C545" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D545" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>CHEMBL1230658</t>
+          <t>CHEMBL1221657</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -12324,7 +12324,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>CHEMBL121790</t>
+          <t>CHEMBL1221659</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -12340,7 +12340,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>CHEMBL483716</t>
+          <t>CHEMBL1221660</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -12356,7 +12356,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>CHEMBL483849</t>
+          <t>CHEMBL1221699</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -12372,7 +12372,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>CHEMBL483995</t>
+          <t>CHEMBL1221702</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -12388,7 +12388,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>CHEMBL484726</t>
+          <t>CHEMBL1229525</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -12404,23 +12404,23 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>CHEMBL484780</t>
+          <t>CHEMBL1229535</t>
         </is>
       </c>
       <c r="B552" t="n">
         <v>1</v>
       </c>
       <c r="C552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D552" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>CHEMBL485323</t>
+          <t>CHEMBL120708</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -12436,7 +12436,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>CHEMBL485835</t>
+          <t>CHEMBL503090</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -12452,7 +12452,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>CHEMBL485945</t>
+          <t>CHEMBL504805</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -12468,23 +12468,23 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>CHEMBL487431</t>
+          <t>CHEMBL510539</t>
         </is>
       </c>
       <c r="B556" t="n">
         <v>1</v>
       </c>
       <c r="C556" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D556" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>CHEMBL48813</t>
+          <t>CHEMBL512172</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -12500,7 +12500,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>CHEMBL490730</t>
+          <t>CHEMBL512283</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -12516,7 +12516,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>CHEMBL490814</t>
+          <t>CHEMBL513225</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -12532,7 +12532,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>CHEMBL490866</t>
+          <t>CHEMBL513425</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -12548,23 +12548,23 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>CHEMBL491429</t>
+          <t>CHEMBL121941</t>
         </is>
       </c>
       <c r="B561" t="n">
         <v>1</v>
       </c>
       <c r="C561" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D561" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>CHEMBL483161</t>
+          <t>CHEMBL527018</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -12580,7 +12580,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>CHEMBL1229851</t>
+          <t>CHEMBL527066</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -12596,39 +12596,39 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>CHEMBL1229855</t>
+          <t>CHEMBL516357</t>
         </is>
       </c>
       <c r="B564" t="n">
         <v>1</v>
       </c>
       <c r="C564" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D564" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>CHEMBL1229914</t>
+          <t>CHEMBL518800</t>
         </is>
       </c>
       <c r="B565" t="n">
         <v>1</v>
       </c>
       <c r="C565" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D565" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>CHEMBL1229989</t>
+          <t>CHEMBL519160</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -12644,7 +12644,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>CHEMBL1230016</t>
+          <t>CHEMBL519939</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -12660,7 +12660,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>CHEMBL506972</t>
+          <t>CHEMBL521105</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -12676,7 +12676,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>CHEMBL509101</t>
+          <t>CHEMBL521703</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -12692,7 +12692,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>CHEMBL493986</t>
+          <t>CHEMBL509485</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -12708,7 +12708,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>CHEMBL495597</t>
+          <t>CHEMBL1210221</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -12724,7 +12724,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>CHEMBL495758</t>
+          <t>CHEMBL121291</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -12740,55 +12740,55 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>CHEMBL496879</t>
+          <t>CHEMBL120293</t>
         </is>
       </c>
       <c r="B573" t="n">
         <v>1</v>
       </c>
       <c r="C573" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D573" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>CHEMBL1221657</t>
+          <t>CHEMBL1204628</t>
         </is>
       </c>
       <c r="B574" t="n">
         <v>1</v>
       </c>
       <c r="C574" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D574" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>CHEMBL1221659</t>
+          <t>CHEMBL1205452</t>
         </is>
       </c>
       <c r="B575" t="n">
         <v>1</v>
       </c>
       <c r="C575" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D575" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>CHEMBL1221660</t>
+          <t>CHEMBL1205948</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -12804,39 +12804,39 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>CHEMBL1221699</t>
+          <t>CHEMBL522891</t>
         </is>
       </c>
       <c r="B577" t="n">
         <v>1</v>
       </c>
       <c r="C577" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D577" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>CHEMBL1221702</t>
+          <t>CHEMBL525194</t>
         </is>
       </c>
       <c r="B578" t="n">
         <v>1</v>
       </c>
       <c r="C578" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D578" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>CHEMBL1229525</t>
+          <t>CHEMBL537968</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -12852,23 +12852,23 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>CHEMBL1229535</t>
+          <t>CHEMBL538937</t>
         </is>
       </c>
       <c r="B580" t="n">
         <v>1</v>
       </c>
       <c r="C580" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D580" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>CHEMBL120708</t>
+          <t>CHEMBL539906</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -12884,55 +12884,55 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>CHEMBL503090</t>
+          <t>CHEMBL522387</t>
         </is>
       </c>
       <c r="B582" t="n">
         <v>1</v>
       </c>
       <c r="C582" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D582" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>CHEMBL504805</t>
+          <t>CHEMBL54277</t>
         </is>
       </c>
       <c r="B583" t="n">
         <v>1</v>
       </c>
       <c r="C583" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D583" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>CHEMBL510539</t>
+          <t>CHEMBL54481</t>
         </is>
       </c>
       <c r="B584" t="n">
         <v>1</v>
       </c>
       <c r="C584" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D584" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>CHEMBL512172</t>
+          <t>CHEMBL549340</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -12948,7 +12948,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>CHEMBL512283</t>
+          <t>CHEMBL549385</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -12964,7 +12964,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>CHEMBL513225</t>
+          <t>CHEMBL549906</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -12980,7 +12980,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>CHEMBL513425</t>
+          <t>CHEMBL550453</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -12996,23 +12996,23 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>CHEMBL121941</t>
+          <t>CHEMBL563327</t>
         </is>
       </c>
       <c r="B589" t="n">
         <v>1</v>
       </c>
       <c r="C589" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D589" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>CHEMBL527018</t>
+          <t>CHEMBL564249</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -13028,7 +13028,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>CHEMBL527066</t>
+          <t>CHEMBL550795</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -13044,23 +13044,23 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>CHEMBL516357</t>
+          <t>CHEMBL554496</t>
         </is>
       </c>
       <c r="B592" t="n">
         <v>1</v>
       </c>
       <c r="C592" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D592" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>CHEMBL518800</t>
+          <t>CHEMBL555205</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -13076,7 +13076,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>CHEMBL519160</t>
+          <t>CHEMBL557915</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -13092,23 +13092,23 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>CHEMBL519939</t>
+          <t>CHEMBL560739</t>
         </is>
       </c>
       <c r="B595" t="n">
         <v>1</v>
       </c>
       <c r="C595" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D595" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>CHEMBL521105</t>
+          <t>CHEMBL561318</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -13124,7 +13124,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>CHEMBL521703</t>
+          <t>CHEMBL561540</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -13140,7 +13140,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>CHEMBL509485</t>
+          <t>CHEMBL561660</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -13156,7 +13156,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>CHEMBL1210221</t>
+          <t>CHEMBL562314</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -13172,7 +13172,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>CHEMBL121291</t>
+          <t>CHEMBL562743</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -13188,7 +13188,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>CHEMBL120293</t>
+          <t>CHEMBL563168</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -13204,39 +13204,39 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>CHEMBL1204628</t>
+          <t>CHEMBL570533</t>
         </is>
       </c>
       <c r="B602" t="n">
         <v>1</v>
       </c>
       <c r="C602" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D602" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>CHEMBL1205452</t>
+          <t>CHEMBL570537</t>
         </is>
       </c>
       <c r="B603" t="n">
         <v>1</v>
       </c>
       <c r="C603" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D603" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>CHEMBL1205948</t>
+          <t>CHEMBL577144</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -13252,39 +13252,39 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>CHEMBL522891</t>
+          <t>CHEMBL582887</t>
         </is>
       </c>
       <c r="B605" t="n">
         <v>1</v>
       </c>
       <c r="C605" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D605" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>CHEMBL525194</t>
+          <t>NIACIN</t>
         </is>
       </c>
       <c r="B606" t="n">
         <v>1</v>
       </c>
       <c r="C606" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D606" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>CHEMBL537968</t>
+          <t>CHEMBL573819</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -13300,23 +13300,23 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>CHEMBL538937</t>
+          <t>CHEMBL62836</t>
         </is>
       </c>
       <c r="B608" t="n">
         <v>1</v>
       </c>
       <c r="C608" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D608" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>CHEMBL539906</t>
+          <t>CHEMBL62897</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -13332,55 +13332,55 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>CHEMBL522387</t>
+          <t>CHEMBL603367</t>
         </is>
       </c>
       <c r="B610" t="n">
         <v>1</v>
       </c>
       <c r="C610" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D610" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>CHEMBL54277</t>
+          <t>CALCIUM CHLORIDE</t>
         </is>
       </c>
       <c r="B611" t="n">
         <v>1</v>
       </c>
       <c r="C611" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D611" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>CHEMBL54481</t>
+          <t>NITRIC OXIDE</t>
         </is>
       </c>
       <c r="B612" t="n">
         <v>1</v>
       </c>
       <c r="C612" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D612" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>CHEMBL549340</t>
+          <t>CHEMBL63859</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -13396,7 +13396,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>CHEMBL549385</t>
+          <t>CHEMBL63895</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -13412,7 +13412,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>CHEMBL549906</t>
+          <t>CHEMBL1198130</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -13428,23 +13428,23 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>CHEMBL550453</t>
+          <t>CHEMBL1198138</t>
         </is>
       </c>
       <c r="B616" t="n">
         <v>1</v>
       </c>
       <c r="C616" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D616" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>CHEMBL563327</t>
+          <t>CHEMBL1198147</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -13460,7 +13460,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>CHEMBL564249</t>
+          <t>CHEMBL1198148</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -13476,7 +13476,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>CHEMBL550795</t>
+          <t>CHEMBL1198191</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -13492,7 +13492,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>CHEMBL554496</t>
+          <t>CHEMBL1198500</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -13508,7 +13508,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>CHEMBL555205</t>
+          <t>CHEMBL1198650</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -13524,7 +13524,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>CHEMBL557915</t>
+          <t>CHEMBL1184499</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -13540,23 +13540,23 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>CHEMBL560739</t>
+          <t>CHEMBL64934</t>
         </is>
       </c>
       <c r="B623" t="n">
         <v>1</v>
       </c>
       <c r="C623" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D623" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>CHEMBL561318</t>
+          <t>CHEMBL65273</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -13572,7 +13572,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>CHEMBL561540</t>
+          <t>CHEMBL119084</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -13588,7 +13588,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>CHEMBL561660</t>
+          <t>CHEMBL1194345</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -13604,7 +13604,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>CHEMBL562314</t>
+          <t>CHEMBL119489</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -13620,23 +13620,23 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>CHEMBL562743</t>
+          <t>CHEMBL6685</t>
         </is>
       </c>
       <c r="B628" t="n">
         <v>1</v>
       </c>
       <c r="C628" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D628" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>CHEMBL563168</t>
+          <t>CHEMBL66907</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -13652,7 +13652,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>CHEMBL570533</t>
+          <t>CHEMBL67158</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -13668,7 +13668,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>CHEMBL570537</t>
+          <t>CHEMBL1197118</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -13684,7 +13684,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>CHEMBL577144</t>
+          <t>CHEMBL117869</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -13700,7 +13700,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>CHEMBL582887</t>
+          <t>CHEMBL1161221</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -13716,23 +13716,23 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>NIACIN</t>
+          <t>CHEMBL1185001</t>
         </is>
       </c>
       <c r="B634" t="n">
         <v>1</v>
       </c>
       <c r="C634" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D634" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>CHEMBL573819</t>
+          <t>CHEMBL1185242</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -13748,55 +13748,55 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>MEGESTROL ACETATE</t>
+          <t>CHEMBL1186230</t>
         </is>
       </c>
       <c r="B636" t="n">
         <v>1</v>
       </c>
       <c r="C636" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D636" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>CHEMBL62836</t>
+          <t>CHEMBL116597</t>
         </is>
       </c>
       <c r="B637" t="n">
         <v>1</v>
       </c>
       <c r="C637" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D637" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>CHEMBL62897</t>
+          <t>CHEMBL71360</t>
         </is>
       </c>
       <c r="B638" t="n">
         <v>1</v>
       </c>
       <c r="C638" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D638" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>CHEMBL603367</t>
+          <t>CHEMBL71611</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -13812,7 +13812,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>CALCIUM CHLORIDE</t>
+          <t>CHEMBL1173</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -13828,23 +13828,23 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>NITRIC OXIDE</t>
+          <t>CHEMBL117651</t>
         </is>
       </c>
       <c r="B641" t="n">
         <v>1</v>
       </c>
       <c r="C641" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D641" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>DESOXYCORTICOSTERONE ACETATE</t>
+          <t>CHEMBL117658</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -13860,7 +13860,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>CHEMBL63859</t>
+          <t>CHEMBL1160756</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -13876,7 +13876,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>CHEMBL63895</t>
+          <t>CHEMBL1161222</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -13892,7 +13892,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>CHEMBL1198130</t>
+          <t>CHEMBL1163074</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -13908,23 +13908,23 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>CHEMBL1198138</t>
+          <t>CHEMBL1163086</t>
         </is>
       </c>
       <c r="B646" t="n">
         <v>1</v>
       </c>
       <c r="C646" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D646" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>CHEMBL1198147</t>
+          <t>CHEMBL78755</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -13940,7 +13940,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>CHEMBL1198148</t>
+          <t>CHEMBL75691</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -13956,23 +13956,23 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>CHEMBL1198191</t>
+          <t>CHEMBL76029</t>
         </is>
       </c>
       <c r="B649" t="n">
         <v>1</v>
       </c>
       <c r="C649" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D649" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>CHEMBL1198500</t>
+          <t>CHEMBL72006</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -13988,7 +13988,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>CHEMBL1198650</t>
+          <t>CHEMBL115220</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -14004,7 +14004,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>CHEMBL1184499</t>
+          <t>CHEMBL115357</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -14020,7 +14020,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>CHEMBL64934</t>
+          <t>CHEMBL1160597</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -14036,7 +14036,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>CHEMBL65273</t>
+          <t>CHEMBL1160619</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -14052,7 +14052,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>CHEMBL119084</t>
+          <t>CHEMBL112953</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -14068,7 +14068,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>CHEMBL1194345</t>
+          <t>CHEMBL113194</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -14084,7 +14084,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>CHEMBL119489</t>
+          <t>CHEMBL113948</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -14100,23 +14100,23 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>CHEMBL6685</t>
+          <t>CHEMBL77961</t>
         </is>
       </c>
       <c r="B658" t="n">
         <v>1</v>
       </c>
       <c r="C658" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D658" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>CHEMBL66907</t>
+          <t>CHEMBL78455</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -14132,7 +14132,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>CHEMBL67158</t>
+          <t>CHEMBL111575</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -14148,7 +14148,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>CHEMBL1197118</t>
+          <t>CHEMBL81273</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -14164,7 +14164,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>CHEMBL117869</t>
+          <t>CHEMBL112834</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -14180,7 +14180,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>CHEMBL1161221</t>
+          <t>CHEMBL112896</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -14196,7 +14196,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>CHEMBL1185001</t>
+          <t>CHEMBL83116</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -14212,7 +14212,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>CHEMBL1185242</t>
+          <t>CHEMBL83547</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -14228,7 +14228,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>CHEMBL1186230</t>
+          <t>CHEMBL109612</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -14244,55 +14244,55 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>CHEMBL116597</t>
+          <t>CHEMBL1098060</t>
         </is>
       </c>
       <c r="B667" t="n">
         <v>1</v>
       </c>
       <c r="C667" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D667" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>CHEMBL71360</t>
+          <t>CHEMBL109822</t>
         </is>
       </c>
       <c r="B668" t="n">
         <v>1</v>
       </c>
       <c r="C668" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D668" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>CHEMBL71611</t>
+          <t>BIOTIN</t>
         </is>
       </c>
       <c r="B669" t="n">
         <v>1</v>
       </c>
       <c r="C669" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D669" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>CHEMBL1173</t>
+          <t>CHEMBL1088762</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -14308,7 +14308,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>CHEMBL117651</t>
+          <t>CHEMBL1090777</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -14324,7 +14324,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>CHEMBL117658</t>
+          <t>CHEMBL1092830</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -14340,7 +14340,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>CHEMBL1160756</t>
+          <t>CHEMBL109367</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -14356,7 +14356,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>CHEMBL1161222</t>
+          <t>CHEMBL86554</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -14372,7 +14372,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>CHEMBL1163074</t>
+          <t>CHEMBL86658</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -14388,7 +14388,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>CHEMBL1163086</t>
+          <t>CHEMBL87580</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -14404,7 +14404,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>CHEMBL78755</t>
+          <t>CHEMBL108483</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -14420,7 +14420,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>CHEMBL75691</t>
+          <t>CHEMBL1088749</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -14436,23 +14436,23 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>CHEMBL76029</t>
+          <t>CHEMBL92404</t>
         </is>
       </c>
       <c r="B679" t="n">
         <v>1</v>
       </c>
       <c r="C679" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D679" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>CHEMBL72006</t>
+          <t>CHEMBL92567</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -14468,7 +14468,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>PREDNISOLONE ACETATE</t>
+          <t>CHEMBL93247</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -14484,23 +14484,23 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>CHEMBL115220</t>
+          <t>CHEMBL1081312</t>
         </is>
       </c>
       <c r="B682" t="n">
         <v>1</v>
       </c>
       <c r="C682" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D682" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>CHEMBL115357</t>
+          <t>CHEMBL1082738</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -14516,7 +14516,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>CHEMBL1160597</t>
+          <t>CHEMBL1083185</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -14532,7 +14532,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>CHEMBL1160619</t>
+          <t>CHEMBL1084102</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -14548,7 +14548,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>CHEMBL112953</t>
+          <t>CHEMBL1084625</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -14564,7 +14564,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>CHEMBL113194</t>
+          <t>CHEMBL100109</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -14580,7 +14580,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>CHEMBL113948</t>
+          <t>CHEMBL99447</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -14596,7 +14596,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>CHEMBL77961</t>
+          <t>CHEMBL104166</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -14612,7 +14612,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>CHEMBL78455</t>
+          <t>CHOLECALCIFEROL</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -14628,7 +14628,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>CHEMBL111575</t>
+          <t>CHEMBL104937</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -14644,7 +14644,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>CHEMBL81273</t>
+          <t>CHEMBL196526</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -14660,7 +14660,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>CHEMBL112834</t>
+          <t>CHEMBL191060</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -14676,23 +14676,23 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>CHEMBL112896</t>
+          <t>CHEMBL101801</t>
         </is>
       </c>
       <c r="B694" t="n">
         <v>1</v>
       </c>
       <c r="C694" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D694" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>CHEMBL83116</t>
+          <t>PYRIDOXAL</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -14708,7 +14708,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>CHEMBL83547</t>
+          <t>CHEMBL103043</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -14718,502 +14718,6 @@
         <v>1</v>
       </c>
       <c r="D696" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
-        <is>
-          <t>CHEMBL109612</t>
-        </is>
-      </c>
-      <c r="B697" t="n">
-        <v>1</v>
-      </c>
-      <c r="C697" t="n">
-        <v>1</v>
-      </c>
-      <c r="D697" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
-        <is>
-          <t>CHEMBL1098060</t>
-        </is>
-      </c>
-      <c r="B698" t="n">
-        <v>1</v>
-      </c>
-      <c r="C698" t="n">
-        <v>2</v>
-      </c>
-      <c r="D698" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
-        <is>
-          <t>CHEMBL109822</t>
-        </is>
-      </c>
-      <c r="B699" t="n">
-        <v>1</v>
-      </c>
-      <c r="C699" t="n">
-        <v>1</v>
-      </c>
-      <c r="D699" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
-        <is>
-          <t>BIOTIN</t>
-        </is>
-      </c>
-      <c r="B700" t="n">
-        <v>1</v>
-      </c>
-      <c r="C700" t="n">
-        <v>8</v>
-      </c>
-      <c r="D700" t="n">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
-        <is>
-          <t>CHEMBL1088762</t>
-        </is>
-      </c>
-      <c r="B701" t="n">
-        <v>1</v>
-      </c>
-      <c r="C701" t="n">
-        <v>1</v>
-      </c>
-      <c r="D701" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
-        <is>
-          <t>CHEMBL1090777</t>
-        </is>
-      </c>
-      <c r="B702" t="n">
-        <v>1</v>
-      </c>
-      <c r="C702" t="n">
-        <v>1</v>
-      </c>
-      <c r="D702" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
-        <is>
-          <t>CHEMBL1092830</t>
-        </is>
-      </c>
-      <c r="B703" t="n">
-        <v>1</v>
-      </c>
-      <c r="C703" t="n">
-        <v>1</v>
-      </c>
-      <c r="D703" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
-        <is>
-          <t>CHEMBL109367</t>
-        </is>
-      </c>
-      <c r="B704" t="n">
-        <v>1</v>
-      </c>
-      <c r="C704" t="n">
-        <v>1</v>
-      </c>
-      <c r="D704" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
-        <is>
-          <t>CHEMBL86554</t>
-        </is>
-      </c>
-      <c r="B705" t="n">
-        <v>1</v>
-      </c>
-      <c r="C705" t="n">
-        <v>1</v>
-      </c>
-      <c r="D705" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>CHEMBL86658</t>
-        </is>
-      </c>
-      <c r="B706" t="n">
-        <v>1</v>
-      </c>
-      <c r="C706" t="n">
-        <v>1</v>
-      </c>
-      <c r="D706" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>CHEMBL87580</t>
-        </is>
-      </c>
-      <c r="B707" t="n">
-        <v>1</v>
-      </c>
-      <c r="C707" t="n">
-        <v>1</v>
-      </c>
-      <c r="D707" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>CHEMBL108483</t>
-        </is>
-      </c>
-      <c r="B708" t="n">
-        <v>1</v>
-      </c>
-      <c r="C708" t="n">
-        <v>1</v>
-      </c>
-      <c r="D708" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>CHEMBL1088749</t>
-        </is>
-      </c>
-      <c r="B709" t="n">
-        <v>1</v>
-      </c>
-      <c r="C709" t="n">
-        <v>1</v>
-      </c>
-      <c r="D709" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
-        <is>
-          <t>CHEMBL92404</t>
-        </is>
-      </c>
-      <c r="B710" t="n">
-        <v>1</v>
-      </c>
-      <c r="C710" t="n">
-        <v>1</v>
-      </c>
-      <c r="D710" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
-        <is>
-          <t>CHEMBL92567</t>
-        </is>
-      </c>
-      <c r="B711" t="n">
-        <v>1</v>
-      </c>
-      <c r="C711" t="n">
-        <v>1</v>
-      </c>
-      <c r="D711" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
-        <is>
-          <t>CHEMBL93247</t>
-        </is>
-      </c>
-      <c r="B712" t="n">
-        <v>1</v>
-      </c>
-      <c r="C712" t="n">
-        <v>1</v>
-      </c>
-      <c r="D712" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
-        <is>
-          <t>CHEMBL1081312</t>
-        </is>
-      </c>
-      <c r="B713" t="n">
-        <v>1</v>
-      </c>
-      <c r="C713" t="n">
-        <v>1</v>
-      </c>
-      <c r="D713" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
-        <is>
-          <t>CHEMBL1082738</t>
-        </is>
-      </c>
-      <c r="B714" t="n">
-        <v>1</v>
-      </c>
-      <c r="C714" t="n">
-        <v>1</v>
-      </c>
-      <c r="D714" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
-        <is>
-          <t>CHEMBL1083185</t>
-        </is>
-      </c>
-      <c r="B715" t="n">
-        <v>1</v>
-      </c>
-      <c r="C715" t="n">
-        <v>1</v>
-      </c>
-      <c r="D715" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
-        <is>
-          <t>CHEMBL1084102</t>
-        </is>
-      </c>
-      <c r="B716" t="n">
-        <v>1</v>
-      </c>
-      <c r="C716" t="n">
-        <v>1</v>
-      </c>
-      <c r="D716" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
-        <is>
-          <t>CHEMBL1084625</t>
-        </is>
-      </c>
-      <c r="B717" t="n">
-        <v>1</v>
-      </c>
-      <c r="C717" t="n">
-        <v>1</v>
-      </c>
-      <c r="D717" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
-        <is>
-          <t>CHEMBL100109</t>
-        </is>
-      </c>
-      <c r="B718" t="n">
-        <v>1</v>
-      </c>
-      <c r="C718" t="n">
-        <v>1</v>
-      </c>
-      <c r="D718" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
-        <is>
-          <t>CHEMBL99447</t>
-        </is>
-      </c>
-      <c r="B719" t="n">
-        <v>1</v>
-      </c>
-      <c r="C719" t="n">
-        <v>1</v>
-      </c>
-      <c r="D719" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
-        <is>
-          <t>CHEMBL104166</t>
-        </is>
-      </c>
-      <c r="B720" t="n">
-        <v>1</v>
-      </c>
-      <c r="C720" t="n">
-        <v>1</v>
-      </c>
-      <c r="D720" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
-        <is>
-          <t>CHOLECALCIFEROL</t>
-        </is>
-      </c>
-      <c r="B721" t="n">
-        <v>1</v>
-      </c>
-      <c r="C721" t="n">
-        <v>1</v>
-      </c>
-      <c r="D721" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
-        <is>
-          <t>CHEMBL104937</t>
-        </is>
-      </c>
-      <c r="B722" t="n">
-        <v>1</v>
-      </c>
-      <c r="C722" t="n">
-        <v>1</v>
-      </c>
-      <c r="D722" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
-        <is>
-          <t>CHEMBL196526</t>
-        </is>
-      </c>
-      <c r="B723" t="n">
-        <v>1</v>
-      </c>
-      <c r="C723" t="n">
-        <v>1</v>
-      </c>
-      <c r="D723" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
-        <is>
-          <t>CHEMBL191060</t>
-        </is>
-      </c>
-      <c r="B724" t="n">
-        <v>1</v>
-      </c>
-      <c r="C724" t="n">
-        <v>1</v>
-      </c>
-      <c r="D724" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
-        <is>
-          <t>CHEMBL101801</t>
-        </is>
-      </c>
-      <c r="B725" t="n">
-        <v>1</v>
-      </c>
-      <c r="C725" t="n">
-        <v>2</v>
-      </c>
-      <c r="D725" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
-        <is>
-          <t>PYRIDOXAL</t>
-        </is>
-      </c>
-      <c r="B726" t="n">
-        <v>1</v>
-      </c>
-      <c r="C726" t="n">
-        <v>1</v>
-      </c>
-      <c r="D726" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
-        <is>
-          <t>CHEMBL103043</t>
-        </is>
-      </c>
-      <c r="B727" t="n">
-        <v>1</v>
-      </c>
-      <c r="C727" t="n">
-        <v>1</v>
-      </c>
-      <c r="D727" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Paper2_Package/03_RESULTS/Task4_drug_coverage/task4_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task4_drug_coverage/task4_supporting.xlsx
@@ -3576,7 +3576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D696"/>
+  <dimension ref="A1:D697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4020,39 +4020,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RETINOL</t>
+          <t>MAGNESIUM SULFATE ANHYDROUS</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>0.267</v>
+        <v>0.444</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHEMBL126506</t>
+          <t>RETINOL</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHEMBL3184454</t>
+          <t>CHEMBL126506</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -4068,7 +4068,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHOLINE</t>
+          <t>CHEMBL3184454</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -4084,39 +4084,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CHEMBL1234619</t>
+          <t>CHOLINE</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHEMBL140</t>
+          <t>CHEMBL1234619</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHEMBL3185220</t>
+          <t>CHEMBL140</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -4132,7 +4132,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CHEMBL3275971</t>
+          <t>CHEMBL3185220</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -4148,279 +4148,279 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CREATINE</t>
+          <t>CHEMBL3275971</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.429</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHEMBL7064</t>
+          <t>CREATINE</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>0.75</v>
+        <v>0.429</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TAURINE</t>
+          <t>CHEMBL7064</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>0.143</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CHEMBL407009</t>
+          <t>TAURINE</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SODIUM CARBONATE</t>
+          <t>CHEMBL407009</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CHEMBL445001</t>
+          <t>SODIUM CARBONATE</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>0.333</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>UREA</t>
+          <t>CHEMBL445001</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHEMBL1080759</t>
+          <t>UREA</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CHEMBL1232920</t>
+          <t>CHEMBL1080759</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CHEMBL1235255</t>
+          <t>CHEMBL1232920</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CHEMBL1235246</t>
+          <t>CHEMBL1235255</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LITHIUM ION</t>
+          <t>CHEMBL1235246</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CHEMBL1235115</t>
+          <t>LITHIUM ION</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CHEMBL388154</t>
+          <t>CHEMBL1235115</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CHEMBL394875</t>
+          <t>CHEMBL388154</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MAGNESIUM ACETATE TETRAHYDRATE</t>
+          <t>CHEMBL394875</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>0.286</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CHEMBL38397</t>
+          <t>MAGNESIUM ACETATE TETRAHYDRATE</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>0.667</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CHEMBL1237210</t>
+          <t>CHEMBL38397</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -4436,23 +4436,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CHEMBL391737</t>
+          <t>CHEMBL1237210</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CHEMBL391640</t>
+          <t>CHEMBL391737</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -4468,215 +4468,215 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ALPHA-TOCOPHEROL</t>
+          <t>CHEMBL391640</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CHEMBL1230790</t>
+          <t>ALPHA-TOCOPHEROL</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHEMBL490225</t>
+          <t>CHEMBL1230790</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CHEMBL383189</t>
+          <t>CHEMBL490225</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CHEMBL1207374</t>
+          <t>CHEMBL383189</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CHEMBL1229585</t>
+          <t>CHEMBL1207374</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CHEMBL486954</t>
+          <t>CHEMBL1229585</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>2</v>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CHEMBL1230513</t>
+          <t>CHEMBL486954</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CHEMBL1230309</t>
+          <t>CHEMBL1230513</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CHEMBL345292</t>
+          <t>CHEMBL1230309</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CHEMBL350239</t>
+          <t>CHEMBL345292</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CHEMBL510038</t>
+          <t>CHEMBL350239</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CHEMBL1213270</t>
+          <t>CHEMBL510038</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CHEMBL1213083</t>
+          <t>CHEMBL1213270</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4692,23 +4692,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CHEMBL1204498</t>
+          <t>CHEMBL1213083</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CHEMBL327715</t>
+          <t>CHEMBL1204498</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4724,119 +4724,119 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CHEMBL146245</t>
+          <t>CHEMBL327715</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>0.125</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CHEMBL283807</t>
+          <t>CHEMBL146245</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D73" t="n">
-        <v>0.286</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CHEMBL286939</t>
+          <t>CHEMBL283807</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D74" t="n">
-        <v>0.667</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MAGNESIUM CARBONATE</t>
+          <t>CHEMBL286939</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>0.286</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CHEMBL260629</t>
+          <t>MAGNESIUM CARBONATE</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D76" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CHEMBL24683</t>
+          <t>CHEMBL260629</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>2</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CHEMBL1161998</t>
+          <t>CHEMBL24683</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>2</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CHEMBL74078</t>
+          <t>CHEMBL1161998</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4852,39 +4852,39 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SUCROSE</t>
+          <t>CHEMBL74078</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SODIUM SULFATE ANHYDROUS</t>
+          <t>SUCROSE</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CHEMBL223026</t>
+          <t>SODIUM SULFATE ANHYDROUS</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -4900,103 +4900,103 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CHEMBL213907</t>
+          <t>CHEMBL223026</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>0.111</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CHEMBL113690</t>
+          <t>CHEMBL213907</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SERINE</t>
+          <t>CHEMBL113690</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>2</v>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>0.286</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CHEMBL21156</t>
+          <t>SERINE</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>2</v>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CHEMBL216543</t>
+          <t>CHEMBL21156</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D87" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CHEMBL180792</t>
+          <t>CHEMBL216543</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CHEMBL180517</t>
+          <t>CHEMBL180792</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -5012,7 +5012,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CHEMBL180071</t>
+          <t>CHEMBL180517</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -5028,71 +5028,71 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CHEMBL96433</t>
+          <t>CHEMBL180071</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CHEMBL193676</t>
+          <t>CHEMBL96433</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>2</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TOCOPHEROL ACETATE</t>
+          <t>CHEMBL193676</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>2</v>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CHEMBL96862</t>
+          <t>TOCOPHEROL ACETATE</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CHEMBL95700</t>
+          <t>CHEMBL96862</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -5108,7 +5108,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CHEMBL93560</t>
+          <t>CHEMBL95700</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -5124,7 +5124,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CHEMBL93647</t>
+          <t>CHEMBL93560</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -5140,7 +5140,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CHEMBL94061</t>
+          <t>CHEMBL93647</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -5156,7 +5156,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CHEMBL94277</t>
+          <t>CHEMBL94061</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -5172,7 +5172,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CHEMBL106708</t>
+          <t>CHEMBL94277</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -5188,7 +5188,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CHEMBL107316</t>
+          <t>CHEMBL106708</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -5204,7 +5204,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CHEMBL191275</t>
+          <t>CHEMBL107316</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -5220,7 +5220,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CHEMBL192894</t>
+          <t>CHEMBL191275</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -5236,7 +5236,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CHEMBL193233</t>
+          <t>CHEMBL192894</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -5252,7 +5252,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CHEMBL194176</t>
+          <t>CHEMBL193233</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -5268,7 +5268,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CHEMBL194805</t>
+          <t>CHEMBL194176</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -5284,7 +5284,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CHEMBL194911</t>
+          <t>CHEMBL194805</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -5300,39 +5300,39 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CHEMBL204997</t>
+          <t>CHEMBL194911</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>1</v>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CHEMBL205437</t>
+          <t>CHEMBL204997</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>1</v>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CHEMBL205786</t>
+          <t>CHEMBL205437</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -5348,7 +5348,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CHEMBL200255</t>
+          <t>CHEMBL205786</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -5364,7 +5364,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CHEMBL200469</t>
+          <t>CHEMBL200255</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -5380,7 +5380,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CHEMBL200495</t>
+          <t>CHEMBL200469</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -5396,7 +5396,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CHEMBL201880</t>
+          <t>CHEMBL200495</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -5412,7 +5412,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CHEMBL202431</t>
+          <t>CHEMBL201880</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -5428,7 +5428,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CHEMBL202609</t>
+          <t>CHEMBL202431</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -5444,7 +5444,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CHEMBL202839</t>
+          <t>CHEMBL202609</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -5460,7 +5460,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CHEMBL207994</t>
+          <t>CHEMBL202839</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -5476,7 +5476,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CHEMBL208239</t>
+          <t>CHEMBL207994</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -5492,71 +5492,71 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CHEMBL2089125</t>
+          <t>CHEMBL208239</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>1</v>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CHEMBL209073</t>
+          <t>CHEMBL2089125</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CHEMBL203407</t>
+          <t>CHEMBL209073</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>1</v>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CHEMBL203517</t>
+          <t>CHEMBL203407</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CHEMBL203631</t>
+          <t>CHEMBL203517</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -5572,7 +5572,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CHEMBL203836</t>
+          <t>CHEMBL203631</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -5588,7 +5588,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CHEMBL204086</t>
+          <t>CHEMBL203836</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -5604,7 +5604,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CHEMBL204459</t>
+          <t>CHEMBL204086</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -5620,39 +5620,39 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CHEMBL189938</t>
+          <t>CHEMBL204459</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CHEMBL190201</t>
+          <t>CHEMBL189938</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CHEMBL190801</t>
+          <t>CHEMBL190201</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -5668,7 +5668,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CHEMBL184444</t>
+          <t>CHEMBL190801</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -5684,39 +5684,39 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CHEMBL207496</t>
+          <t>CHEMBL184444</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CHEMBL207701</t>
+          <t>CHEMBL207496</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CHEMBL207729</t>
+          <t>CHEMBL207701</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -5732,7 +5732,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CHEMBL185097</t>
+          <t>CHEMBL207729</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -5748,7 +5748,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CHEMBL18591</t>
+          <t>CHEMBL185097</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -5764,7 +5764,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CHEMBL188865</t>
+          <t>CHEMBL18591</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -5780,7 +5780,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CHEMBL205821</t>
+          <t>CHEMBL188865</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -5796,39 +5796,39 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CHEMBL207228</t>
+          <t>CHEMBL205821</t>
         </is>
       </c>
       <c r="B139" t="n">
         <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CHEMBL189434</t>
+          <t>CHEMBL207228</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>1</v>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CHEMBL18136</t>
+          <t>CHEMBL189434</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -5844,7 +5844,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CHEMBL181936</t>
+          <t>CHEMBL18136</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -5860,7 +5860,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CHEMBL182323</t>
+          <t>CHEMBL181936</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -5876,55 +5876,55 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CHEMBL184151</t>
+          <t>CHEMBL182323</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CHEMBL209740</t>
+          <t>CHEMBL184151</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>1</v>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CHEMBL180300</t>
+          <t>CHEMBL209740</t>
         </is>
       </c>
       <c r="B146" t="n">
         <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CHEMBL178090</t>
+          <t>CHEMBL180300</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -5940,7 +5940,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CHEMBL178130</t>
+          <t>CHEMBL178090</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -5956,7 +5956,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CHEMBL178938</t>
+          <t>CHEMBL178130</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -5972,7 +5972,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CHEMBL217914</t>
+          <t>CHEMBL178938</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -5988,7 +5988,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CHEMBL218006</t>
+          <t>CHEMBL217914</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -6004,7 +6004,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CHEMBL174539</t>
+          <t>CHEMBL218006</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -6020,7 +6020,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CHEMBL175198</t>
+          <t>CHEMBL174539</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -6036,7 +6036,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CHEMBL169526</t>
+          <t>CHEMBL175198</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -6052,7 +6052,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CHEMBL213758</t>
+          <t>CHEMBL169526</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -6068,7 +6068,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CHEMBL214502</t>
+          <t>CHEMBL213758</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -6084,7 +6084,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CHEMBL215344</t>
+          <t>CHEMBL214502</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -6100,7 +6100,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CHEMBL216697</t>
+          <t>CHEMBL215344</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -6116,39 +6116,39 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CHEMBL223339</t>
+          <t>CHEMBL216697</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>1</v>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CHEMBL223512</t>
+          <t>CHEMBL223339</t>
         </is>
       </c>
       <c r="B160" t="n">
         <v>1</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CHEMBL218289</t>
+          <t>CHEMBL223512</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -6164,7 +6164,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CHEMBL218382</t>
+          <t>CHEMBL218289</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -6180,7 +6180,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CHEMBL219484</t>
+          <t>CHEMBL218382</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -6196,39 +6196,39 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CHEMBL220320</t>
+          <t>CHEMBL219484</t>
         </is>
       </c>
       <c r="B164" t="n">
         <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CHEMBL220467</t>
+          <t>CHEMBL220320</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>1</v>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CHEMBL220513</t>
+          <t>CHEMBL220467</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -6244,7 +6244,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CHEMBL220529</t>
+          <t>CHEMBL220513</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -6260,7 +6260,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHEMBL212616</t>
+          <t>CHEMBL220529</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -6276,7 +6276,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CHEMBL221735</t>
+          <t>CHEMBL212616</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -6292,7 +6292,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CHEMBL223147</t>
+          <t>CHEMBL221735</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -6308,7 +6308,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CHEMBL223873</t>
+          <t>CHEMBL223147</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -6324,7 +6324,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CHEMBL225210</t>
+          <t>CHEMBL223873</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -6340,7 +6340,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CHEMBL225664</t>
+          <t>CHEMBL225210</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -6356,23 +6356,23 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CHEMBL226403</t>
+          <t>CHEMBL225664</t>
         </is>
       </c>
       <c r="B174" t="n">
         <v>1</v>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CHEMBL226471</t>
+          <t>CHEMBL226403</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -6388,23 +6388,23 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CHEMBL221181</t>
+          <t>CHEMBL226471</t>
         </is>
       </c>
       <c r="B176" t="n">
         <v>1</v>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CHEMBL233360</t>
+          <t>CHEMBL221181</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -6420,23 +6420,23 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CHEMBL233553</t>
+          <t>CHEMBL233360</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>1</v>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CHEMBL233970</t>
+          <t>CHEMBL233553</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -6452,87 +6452,87 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CHEMBL233992</t>
+          <t>CHEMBL233970</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>1</v>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CHEMBL227381</t>
+          <t>CHEMBL233992</t>
         </is>
       </c>
       <c r="B181" t="n">
         <v>1</v>
       </c>
       <c r="C181" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CHEMBL227924</t>
+          <t>CHEMBL227381</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D182" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CHEMBL227954</t>
+          <t>CHEMBL227924</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>1</v>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CHEMBL228133</t>
+          <t>CHEMBL227954</t>
         </is>
       </c>
       <c r="B184" t="n">
         <v>1</v>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CHEMBL228224</t>
+          <t>CHEMBL228133</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -6548,39 +6548,39 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CHEMBL228369</t>
+          <t>CHEMBL228224</t>
         </is>
       </c>
       <c r="B186" t="n">
         <v>1</v>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CHEMBL229855</t>
+          <t>CHEMBL228369</t>
         </is>
       </c>
       <c r="B187" t="n">
         <v>1</v>
       </c>
       <c r="C187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CHEMBL230153</t>
+          <t>CHEMBL229855</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -6596,71 +6596,71 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CHEMBL230910</t>
+          <t>CHEMBL230153</t>
         </is>
       </c>
       <c r="B189" t="n">
         <v>1</v>
       </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D189" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CHEMBL165372</t>
+          <t>CHEMBL230910</t>
         </is>
       </c>
       <c r="B190" t="n">
         <v>1</v>
       </c>
       <c r="C190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FOLIC ACID</t>
+          <t>CHEMBL165372</t>
         </is>
       </c>
       <c r="B191" t="n">
         <v>1</v>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D191" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CHEMBL232566</t>
+          <t>FOLIC ACID</t>
         </is>
       </c>
       <c r="B192" t="n">
         <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CHEMBL232827</t>
+          <t>CHEMBL232566</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -6676,7 +6676,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CHEMBL232942</t>
+          <t>CHEMBL232827</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -6692,71 +6692,71 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CHEMBL233149</t>
+          <t>CHEMBL232942</t>
         </is>
       </c>
       <c r="B195" t="n">
         <v>1</v>
       </c>
       <c r="C195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D195" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CHEMBL233209</t>
+          <t>CHEMBL233149</t>
         </is>
       </c>
       <c r="B196" t="n">
         <v>1</v>
       </c>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CHEMBL233349</t>
+          <t>CHEMBL233209</t>
         </is>
       </c>
       <c r="B197" t="n">
         <v>1</v>
       </c>
       <c r="C197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CHEMBL242737</t>
+          <t>CHEMBL233349</t>
         </is>
       </c>
       <c r="B198" t="n">
         <v>1</v>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D198" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CHEMBL243024</t>
+          <t>CHEMBL242737</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -6772,71 +6772,71 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CHEMBL236086</t>
+          <t>CHEMBL243024</t>
         </is>
       </c>
       <c r="B200" t="n">
         <v>1</v>
       </c>
       <c r="C200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>CHEMBL236708</t>
+          <t>CHEMBL236086</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>1</v>
       </c>
       <c r="C201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CHEMBL236718</t>
+          <t>CHEMBL236708</t>
         </is>
       </c>
       <c r="B202" t="n">
         <v>1</v>
       </c>
       <c r="C202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CHEMBL237337</t>
+          <t>CHEMBL236718</t>
         </is>
       </c>
       <c r="B203" t="n">
         <v>1</v>
       </c>
       <c r="C203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CHEMBL237600</t>
+          <t>CHEMBL237337</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -6852,7 +6852,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CHEMBL237786</t>
+          <t>CHEMBL237600</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -6868,7 +6868,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CHEMBL239507</t>
+          <t>CHEMBL237786</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -6884,7 +6884,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>CHEMBL239508</t>
+          <t>CHEMBL239507</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -6900,7 +6900,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CHEMBL240355</t>
+          <t>CHEMBL239508</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -6916,7 +6916,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>CHEMBL240719</t>
+          <t>CHEMBL240355</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -6932,7 +6932,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>CHEMBL240725</t>
+          <t>CHEMBL240719</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -6948,7 +6948,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CHEMBL241577</t>
+          <t>CHEMBL240725</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -6964,7 +6964,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>CHEMBL242237</t>
+          <t>CHEMBL241577</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -6980,7 +6980,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CHEMBL243731</t>
+          <t>CHEMBL242237</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -6996,7 +6996,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CHEMBL243940</t>
+          <t>CHEMBL243731</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -7012,7 +7012,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CHEMBL243978</t>
+          <t>CHEMBL243940</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -7028,7 +7028,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CHEMBL245678</t>
+          <t>CHEMBL243978</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -7044,7 +7044,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CHEMBL247272</t>
+          <t>CHEMBL245678</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -7060,7 +7060,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Phosphoric Acid Cyclohexylmethyl Ester 2-Formyl-Phenyl Ester</t>
+          <t>CHEMBL247272</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -7076,7 +7076,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CHEMBL248176</t>
+          <t>Phosphoric Acid Cyclohexylmethyl Ester 2-Formyl-Phenyl Ester</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -7092,7 +7092,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CHEMBL248643</t>
+          <t>CHEMBL248176</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -7108,7 +7108,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>CHEMBL24957</t>
+          <t>CHEMBL248643</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -7124,7 +7124,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Mannitol Bis-Phosphate</t>
+          <t>CHEMBL24957</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -7140,7 +7140,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CHEMBL250409</t>
+          <t>Mannitol Bis-Phosphate</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -7156,7 +7156,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CHEMBL250787</t>
+          <t>CHEMBL250409</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -7172,7 +7172,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CHEMBL25186</t>
+          <t>CHEMBL250787</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -7188,7 +7188,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CHEMBL252967</t>
+          <t>CHEMBL25186</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -7204,7 +7204,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CHEMBL253608</t>
+          <t>CHEMBL252967</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -7220,7 +7220,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CHEMBL253825</t>
+          <t>CHEMBL253608</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -7236,7 +7236,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CHEMBL257543</t>
+          <t>CHEMBL253825</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -7252,7 +7252,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CHEMBL257626</t>
+          <t>CHEMBL257543</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -7268,7 +7268,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CHEMBL272114</t>
+          <t>CHEMBL257626</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -7284,7 +7284,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>CHEMBL272198</t>
+          <t>CHEMBL272114</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -7300,7 +7300,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>CHEMBL259420</t>
+          <t>CHEMBL272198</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -7316,103 +7316,103 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CHEMBL260000</t>
+          <t>CHEMBL259420</t>
         </is>
       </c>
       <c r="B234" t="n">
         <v>1</v>
       </c>
       <c r="C234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D234" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>CHEMBL262628</t>
+          <t>CHEMBL260000</t>
         </is>
       </c>
       <c r="B235" t="n">
         <v>1</v>
       </c>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CHEMBL254520</t>
+          <t>CHEMBL262628</t>
         </is>
       </c>
       <c r="B236" t="n">
         <v>1</v>
       </c>
       <c r="C236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CHEMBL159820</t>
+          <t>CHEMBL254520</t>
         </is>
       </c>
       <c r="B237" t="n">
         <v>1</v>
       </c>
       <c r="C237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D237" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>CHEMBL270672</t>
+          <t>CHEMBL159820</t>
         </is>
       </c>
       <c r="B238" t="n">
         <v>1</v>
       </c>
       <c r="C238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D238" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CHEMBL271138</t>
+          <t>CHEMBL270672</t>
         </is>
       </c>
       <c r="B239" t="n">
         <v>1</v>
       </c>
       <c r="C239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CHEMBL157105</t>
+          <t>CHEMBL271138</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -7428,7 +7428,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CHEMBL273822</t>
+          <t>CHEMBL157105</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -7444,7 +7444,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CHEMBL275339</t>
+          <t>CHEMBL273822</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -7460,7 +7460,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CHEMBL267048</t>
+          <t>CHEMBL275339</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -7476,7 +7476,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CHEMBL282837</t>
+          <t>CHEMBL267048</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -7492,7 +7492,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CHEMBL27784</t>
+          <t>CHEMBL282837</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -7508,39 +7508,39 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>RIBOFLAVIN</t>
+          <t>CHEMBL27784</t>
         </is>
       </c>
       <c r="B246" t="n">
         <v>1</v>
       </c>
       <c r="C246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D246" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CHEMBL149502</t>
+          <t>RIBOFLAVIN</t>
         </is>
       </c>
       <c r="B247" t="n">
         <v>1</v>
       </c>
       <c r="C247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D247" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CHEMBL149603</t>
+          <t>CHEMBL149502</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -7556,7 +7556,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CHEMBL1513348</t>
+          <t>CHEMBL149603</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -7572,7 +7572,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>CHEMBL281795</t>
+          <t>CHEMBL1513348</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -7588,7 +7588,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CHEMBL282146</t>
+          <t>CHEMBL281795</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -7604,39 +7604,39 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>CHEMBL148333</t>
+          <t>CHEMBL282146</t>
         </is>
       </c>
       <c r="B252" t="n">
         <v>1</v>
       </c>
       <c r="C252" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D252" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Phosphoric Acid Benzyl Ester 2-Formyl-Phenyl Ester</t>
+          <t>CHEMBL148333</t>
         </is>
       </c>
       <c r="B253" t="n">
         <v>1</v>
       </c>
       <c r="C253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D253" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CHEMBL148732</t>
+          <t>Phosphoric Acid Benzyl Ester 2-Formyl-Phenyl Ester</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -7652,7 +7652,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CHEMBL148756</t>
+          <t>CHEMBL148732</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -7668,7 +7668,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CHEMBL286364</t>
+          <t>CHEMBL148756</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -7684,7 +7684,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CHEMBL286678</t>
+          <t>CHEMBL286364</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -7700,7 +7700,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CHEMBL289422</t>
+          <t>CHEMBL286678</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -7716,7 +7716,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CHEMBL291678</t>
+          <t>CHEMBL289422</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -7732,71 +7732,71 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CHEMBL292821</t>
+          <t>CHEMBL291678</t>
         </is>
       </c>
       <c r="B260" t="n">
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D260" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>CHEMBL293034</t>
+          <t>CHEMBL292821</t>
         </is>
       </c>
       <c r="B261" t="n">
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D261" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>CHEMBL293212</t>
+          <t>CHEMBL293034</t>
         </is>
       </c>
       <c r="B262" t="n">
         <v>1</v>
       </c>
       <c r="C262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D262" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>CHEMBL142996</t>
+          <t>CHEMBL293212</t>
         </is>
       </c>
       <c r="B263" t="n">
         <v>1</v>
       </c>
       <c r="C263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D263" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>CHEMBL296323</t>
+          <t>CHEMBL142996</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -7812,71 +7812,71 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CHEMBL298445</t>
+          <t>CHEMBL296323</t>
         </is>
       </c>
       <c r="B265" t="n">
         <v>1</v>
       </c>
       <c r="C265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D265" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CHEMBL302715</t>
+          <t>CHEMBL298445</t>
         </is>
       </c>
       <c r="B266" t="n">
         <v>1</v>
       </c>
       <c r="C266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D266" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>CHEMBL303992</t>
+          <t>CHEMBL302715</t>
         </is>
       </c>
       <c r="B267" t="n">
         <v>1</v>
       </c>
       <c r="C267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D267" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CHEMBL304552</t>
+          <t>CHEMBL303992</t>
         </is>
       </c>
       <c r="B268" t="n">
         <v>1</v>
       </c>
       <c r="C268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D268" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>CHEMBL305785</t>
+          <t>CHEMBL304552</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -7892,39 +7892,39 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CHEMBL306380</t>
+          <t>CHEMBL305785</t>
         </is>
       </c>
       <c r="B270" t="n">
         <v>1</v>
       </c>
       <c r="C270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D270" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>CHEMBL295971</t>
+          <t>CHEMBL306380</t>
         </is>
       </c>
       <c r="B271" t="n">
         <v>1</v>
       </c>
       <c r="C271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D271" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CHEMBL141889</t>
+          <t>CHEMBL295971</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -7940,7 +7940,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CHEMBL309282</t>
+          <t>CHEMBL141889</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -7956,7 +7956,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>CHEMBL310554</t>
+          <t>CHEMBL309282</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -7972,39 +7972,39 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CHEMBL311228</t>
+          <t>CHEMBL310554</t>
         </is>
       </c>
       <c r="B275" t="n">
         <v>1</v>
       </c>
       <c r="C275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D275" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>CHEMBL316053</t>
+          <t>CHEMBL311228</t>
         </is>
       </c>
       <c r="B276" t="n">
         <v>1</v>
       </c>
       <c r="C276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D276" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>CHEMBL316388</t>
+          <t>CHEMBL316053</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -8020,7 +8020,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>CHEMBL3185126</t>
+          <t>CHEMBL316388</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -8036,55 +8036,55 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>CHEMBL3185133</t>
+          <t>CHEMBL3185126</t>
         </is>
       </c>
       <c r="B279" t="n">
         <v>1</v>
       </c>
       <c r="C279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D279" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>CHEMBL3186422</t>
+          <t>CHEMBL3185133</t>
         </is>
       </c>
       <c r="B280" t="n">
         <v>1</v>
       </c>
       <c r="C280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D280" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>CHEMBL318721</t>
+          <t>CHEMBL3186422</t>
         </is>
       </c>
       <c r="B281" t="n">
         <v>1</v>
       </c>
       <c r="C281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D281" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>CHEMBL329433</t>
+          <t>CHEMBL318721</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -8100,7 +8100,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>CHEMBL329985</t>
+          <t>CHEMBL329433</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -8116,7 +8116,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CHEMBL319516</t>
+          <t>CHEMBL329985</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -8132,7 +8132,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CHEMBL321130</t>
+          <t>CHEMBL319516</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -8148,7 +8148,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CHEMBL321944</t>
+          <t>CHEMBL321130</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -8164,23 +8164,23 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>CHEMBL323556</t>
+          <t>CHEMBL321944</t>
         </is>
       </c>
       <c r="B287" t="n">
         <v>1</v>
       </c>
       <c r="C287" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D287" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>CHEMBL323668</t>
+          <t>CHEMBL323556</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -8196,23 +8196,23 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>CHEMBL324168</t>
+          <t>CHEMBL323668</t>
         </is>
       </c>
       <c r="B289" t="n">
         <v>1</v>
       </c>
       <c r="C289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D289" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>CHEMBL138806</t>
+          <t>CHEMBL324168</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -8228,7 +8228,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>CHEMBL139393</t>
+          <t>CHEMBL138806</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -8244,7 +8244,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>CHEMBL139423</t>
+          <t>CHEMBL139393</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -8260,7 +8260,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>CHEMBL326082</t>
+          <t>CHEMBL139423</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -8276,7 +8276,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>CHEMBL326523</t>
+          <t>CHEMBL326082</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -8292,7 +8292,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>CHEMBL326564</t>
+          <t>CHEMBL326523</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -8308,7 +8308,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>CHEMBL326651</t>
+          <t>CHEMBL326564</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -8324,7 +8324,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>CHEMBL328139</t>
+          <t>CHEMBL326651</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -8340,7 +8340,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>CHEMBL328827</t>
+          <t>CHEMBL328139</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -8356,7 +8356,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>CHEMBL331282</t>
+          <t>CHEMBL328827</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -8372,7 +8372,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CHEMBL332935</t>
+          <t>CHEMBL331282</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -8388,7 +8388,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>CHEMBL334167</t>
+          <t>CHEMBL332935</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -8404,7 +8404,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>CHEMBL324951</t>
+          <t>CHEMBL334167</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -8420,7 +8420,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>CHEMBL325029</t>
+          <t>CHEMBL324951</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -8436,7 +8436,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>CHEMBL336908</t>
+          <t>CHEMBL325029</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -8452,7 +8452,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>CHEMBL338076</t>
+          <t>CHEMBL336908</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -8468,71 +8468,71 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>CHEMBL339611</t>
+          <t>CHEMBL338076</t>
         </is>
       </c>
       <c r="B306" t="n">
         <v>1</v>
       </c>
       <c r="C306" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D306" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CHEMBL34062</t>
+          <t>CHEMBL339611</t>
         </is>
       </c>
       <c r="B307" t="n">
         <v>1</v>
       </c>
       <c r="C307" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D307" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>CHEMBL341273</t>
+          <t>CHEMBL34062</t>
         </is>
       </c>
       <c r="B308" t="n">
         <v>1</v>
       </c>
       <c r="C308" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D308" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>CHEMBL342478</t>
+          <t>CHEMBL341273</t>
         </is>
       </c>
       <c r="B309" t="n">
         <v>1</v>
       </c>
       <c r="C309" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D309" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CHEMBL343336</t>
+          <t>CHEMBL342478</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -8548,7 +8548,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>CHEMBL135287</t>
+          <t>CHEMBL343336</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -8564,39 +8564,39 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>CHEMBL1313657</t>
+          <t>CHEMBL135287</t>
         </is>
       </c>
       <c r="B312" t="n">
         <v>1</v>
       </c>
       <c r="C312" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D312" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>CHEMBL35107</t>
+          <t>CHEMBL1313657</t>
         </is>
       </c>
       <c r="B313" t="n">
         <v>1</v>
       </c>
       <c r="C313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>CHEMBL351298</t>
+          <t>CHEMBL35107</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -8612,7 +8612,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>CHEMBL363847</t>
+          <t>CHEMBL351298</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -8628,7 +8628,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>CHEMBL364748</t>
+          <t>CHEMBL363847</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -8644,7 +8644,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CHEMBL355497</t>
+          <t>CHEMBL364748</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -8660,39 +8660,39 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>CHEMBL3559901</t>
+          <t>CHEMBL355497</t>
         </is>
       </c>
       <c r="B318" t="n">
         <v>1</v>
       </c>
       <c r="C318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D318" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>CHEMBL356002</t>
+          <t>CHEMBL3559901</t>
         </is>
       </c>
       <c r="B319" t="n">
         <v>1</v>
       </c>
       <c r="C319" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D319" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>CHEMBL356752</t>
+          <t>CHEMBL356002</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -8708,7 +8708,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>CHEMBL357488</t>
+          <t>CHEMBL356752</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -8724,7 +8724,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>CHEMBL359482</t>
+          <t>CHEMBL357488</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -8740,7 +8740,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>CHEMBL360356</t>
+          <t>CHEMBL359482</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -8756,39 +8756,39 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CHEMBL360520</t>
+          <t>CHEMBL360356</t>
         </is>
       </c>
       <c r="B324" t="n">
         <v>1</v>
       </c>
       <c r="C324" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D324" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>CHEMBL360563</t>
+          <t>CHEMBL360520</t>
         </is>
       </c>
       <c r="B325" t="n">
         <v>1</v>
       </c>
       <c r="C325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D325" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>CHEMBL360998</t>
+          <t>CHEMBL360563</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -8804,7 +8804,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>CHEMBL361078</t>
+          <t>CHEMBL360998</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -8820,7 +8820,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>CHEMBL363302</t>
+          <t>CHEMBL361078</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -8836,39 +8836,39 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>CHEMBL376388</t>
+          <t>CHEMBL363302</t>
         </is>
       </c>
       <c r="B329" t="n">
         <v>1</v>
       </c>
       <c r="C329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D329" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>CHEMBL364811</t>
+          <t>CHEMBL376388</t>
         </is>
       </c>
       <c r="B330" t="n">
         <v>1</v>
       </c>
       <c r="C330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D330" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>CHEMBL366312</t>
+          <t>CHEMBL364811</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -8884,7 +8884,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>CHEMBL368238</t>
+          <t>CHEMBL366312</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -8900,7 +8900,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CHEMBL358860</t>
+          <t>CHEMBL368238</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -8916,7 +8916,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>CHEMBL358866</t>
+          <t>CHEMBL358860</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -8932,7 +8932,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>CHEMBL379692</t>
+          <t>CHEMBL358866</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -8948,7 +8948,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>CHEMBL380589</t>
+          <t>CHEMBL379692</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -8964,7 +8964,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>CHEMBL380888</t>
+          <t>CHEMBL380589</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -8980,7 +8980,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>CHEMBL380955</t>
+          <t>CHEMBL380888</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -8996,7 +8996,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>CHEMBL371732</t>
+          <t>CHEMBL380955</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -9012,39 +9012,39 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>CHEMBL372164</t>
+          <t>CHEMBL371732</t>
         </is>
       </c>
       <c r="B340" t="n">
         <v>1</v>
       </c>
       <c r="C340" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D340" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>CHEMBL373357</t>
+          <t>CHEMBL372164</t>
         </is>
       </c>
       <c r="B341" t="n">
         <v>1</v>
       </c>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D341" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>CHEMBL374713</t>
+          <t>CHEMBL373357</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -9060,7 +9060,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>CHEMBL374936</t>
+          <t>CHEMBL374713</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -9076,7 +9076,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>CHEMBL375112</t>
+          <t>CHEMBL374936</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -9092,7 +9092,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>CHEMBL126589</t>
+          <t>CHEMBL375112</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -9108,39 +9108,39 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>CHEMBL377956</t>
+          <t>CHEMBL126589</t>
         </is>
       </c>
       <c r="B346" t="n">
         <v>1</v>
       </c>
       <c r="C346" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D346" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>CHEMBL378160</t>
+          <t>CHEMBL377956</t>
         </is>
       </c>
       <c r="B347" t="n">
         <v>1</v>
       </c>
       <c r="C347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D347" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>CHEMBL385711</t>
+          <t>CHEMBL378160</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -9156,7 +9156,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>CHEMBL385937</t>
+          <t>CHEMBL385711</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -9172,7 +9172,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>CHEMBL381806</t>
+          <t>CHEMBL385937</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -9188,7 +9188,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CHEMBL382311</t>
+          <t>CHEMBL381806</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -9204,71 +9204,71 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>CHEMBL382639</t>
+          <t>CHEMBL382311</t>
         </is>
       </c>
       <c r="B352" t="n">
         <v>1</v>
       </c>
       <c r="C352" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D352" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ALUMINUM CHLORIDE</t>
+          <t>CHEMBL382639</t>
         </is>
       </c>
       <c r="B353" t="n">
         <v>1</v>
       </c>
       <c r="C353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D353" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>CHEMBL383541</t>
+          <t>ALUMINUM CHLORIDE</t>
         </is>
       </c>
       <c r="B354" t="n">
         <v>1</v>
       </c>
       <c r="C354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D354" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>CHEMBL383570</t>
+          <t>CHEMBL383541</t>
         </is>
       </c>
       <c r="B355" t="n">
         <v>1</v>
       </c>
       <c r="C355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>CHEMBL383705</t>
+          <t>CHEMBL383570</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -9284,7 +9284,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>CHEMBL376632</t>
+          <t>CHEMBL383705</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -9300,7 +9300,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>CHEMBL377312</t>
+          <t>CHEMBL376632</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -9316,7 +9316,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>CHEMBL124493</t>
+          <t>CHEMBL377312</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -9332,7 +9332,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>CHEMBL124718</t>
+          <t>CHEMBL124493</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -9348,7 +9348,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>CHEMBL125236</t>
+          <t>CHEMBL124718</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -9364,7 +9364,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>CHEMBL125381</t>
+          <t>CHEMBL125236</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -9380,7 +9380,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>CHEMBL125386</t>
+          <t>CHEMBL125381</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -9396,7 +9396,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>CHEMBL383990</t>
+          <t>CHEMBL125386</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -9412,7 +9412,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CHEMBL385178</t>
+          <t>CHEMBL383990</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -9428,7 +9428,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>CHEMBL385587</t>
+          <t>CHEMBL385178</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -9444,7 +9444,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>CHEMBL398346</t>
+          <t>CHEMBL385587</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -9460,7 +9460,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>CHEMBL390674</t>
+          <t>CHEMBL398346</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -9476,7 +9476,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>CHEMBL391805</t>
+          <t>CHEMBL390674</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -9492,7 +9492,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>CHEMBL391910</t>
+          <t>CHEMBL391805</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -9508,7 +9508,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>CHEMBL3924132</t>
+          <t>CHEMBL391910</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -9524,7 +9524,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>CHEMBL392452</t>
+          <t>CHEMBL3924132</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -9540,7 +9540,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>CHEMBL392990</t>
+          <t>CHEMBL392452</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -9556,7 +9556,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>CHEMBL383921</t>
+          <t>CHEMBL392990</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -9572,7 +9572,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>CHEMBL398940</t>
+          <t>CHEMBL383921</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -9588,7 +9588,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>CHEMBL399598</t>
+          <t>CHEMBL398940</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -9604,7 +9604,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>CHEMBL400431</t>
+          <t>CHEMBL399598</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -9620,7 +9620,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>CHEMBL400841</t>
+          <t>CHEMBL400431</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -9636,7 +9636,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>CHEMBL393949</t>
+          <t>CHEMBL400841</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -9652,7 +9652,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>CHEMBL394484</t>
+          <t>CHEMBL393949</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -9668,7 +9668,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>CHEMBL3945401</t>
+          <t>CHEMBL394484</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -9684,7 +9684,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>CHEMBL394826</t>
+          <t>CHEMBL3945401</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -9700,7 +9700,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>CHEMBL395280</t>
+          <t>CHEMBL394826</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -9716,7 +9716,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>CHEMBL395347</t>
+          <t>CHEMBL395280</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -9732,7 +9732,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>CHEMBL396380</t>
+          <t>CHEMBL395347</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -9748,7 +9748,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>CHEMBL398428</t>
+          <t>CHEMBL396380</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -9764,7 +9764,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>CHEMBL1235806</t>
+          <t>CHEMBL398428</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -9780,7 +9780,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>CHEMBL1236157</t>
+          <t>CHEMBL1235806</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -9796,7 +9796,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>CHEMBL1236215</t>
+          <t>CHEMBL1236157</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -9812,7 +9812,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>CHEMBL1236268</t>
+          <t>CHEMBL1236215</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -9828,7 +9828,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>CHEMBL1236302</t>
+          <t>CHEMBL1236268</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -9844,71 +9844,71 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>CHEMBL1236433</t>
+          <t>CHEMBL1236302</t>
         </is>
       </c>
       <c r="B392" t="n">
         <v>1</v>
       </c>
       <c r="C392" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D392" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>CHEMBL408967</t>
+          <t>CHEMBL1236433</t>
         </is>
       </c>
       <c r="B393" t="n">
         <v>1</v>
       </c>
       <c r="C393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D393" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>CHEMBL41036</t>
+          <t>CHEMBL408967</t>
         </is>
       </c>
       <c r="B394" t="n">
         <v>1</v>
       </c>
       <c r="C394" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D394" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>CHEMBL401150</t>
+          <t>CHEMBL41036</t>
         </is>
       </c>
       <c r="B395" t="n">
         <v>1</v>
       </c>
       <c r="C395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D395" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>CHEMBL401365</t>
+          <t>CHEMBL401150</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -9924,7 +9924,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>CHEMBL401842</t>
+          <t>CHEMBL401365</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -9940,7 +9940,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>CHEMBL402262</t>
+          <t>CHEMBL401842</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -9956,7 +9956,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>CHEMBL402747</t>
+          <t>CHEMBL402262</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -9972,7 +9972,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>CHEMBL402761</t>
+          <t>CHEMBL402747</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -9988,7 +9988,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>CHEMBL404630</t>
+          <t>CHEMBL402761</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -10004,39 +10004,39 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>PYRIDOXAMINE PHOSPHATE ANHYDROUS</t>
+          <t>CHEMBL404630</t>
         </is>
       </c>
       <c r="B402" t="n">
         <v>1</v>
       </c>
       <c r="C402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D402" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>CHEMBL1235380</t>
+          <t>PYRIDOXAMINE PHOSPHATE ANHYDROUS</t>
         </is>
       </c>
       <c r="B403" t="n">
         <v>1</v>
       </c>
       <c r="C403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D403" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>CHEMBL1235423</t>
+          <t>CHEMBL1235380</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -10052,7 +10052,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>CHEMBL1235556</t>
+          <t>CHEMBL1235423</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -10068,7 +10068,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>CHEMBL1235676</t>
+          <t>CHEMBL1235556</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -10084,7 +10084,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CHEMBL1235693</t>
+          <t>CHEMBL1235676</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -10100,7 +10100,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>CHEMBL1235702</t>
+          <t>CHEMBL1235693</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -10116,103 +10116,103 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>CHEMBL1234624</t>
+          <t>CHEMBL1235702</t>
         </is>
       </c>
       <c r="B409" t="n">
         <v>1</v>
       </c>
       <c r="C409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D409" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>CHEMBL406572</t>
+          <t>CHEMBL1234624</t>
         </is>
       </c>
       <c r="B410" t="n">
         <v>1</v>
       </c>
       <c r="C410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D410" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>CHEMBL406863</t>
+          <t>CHEMBL406572</t>
         </is>
       </c>
       <c r="B411" t="n">
         <v>1</v>
       </c>
       <c r="C411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D411" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>CHEMBL42039</t>
+          <t>CHEMBL406863</t>
         </is>
       </c>
       <c r="B412" t="n">
         <v>1</v>
       </c>
       <c r="C412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D412" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CHEMBL420671</t>
+          <t>CHEMBL42039</t>
         </is>
       </c>
       <c r="B413" t="n">
         <v>1</v>
       </c>
       <c r="C413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D413" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>CHEMBL421138</t>
+          <t>CHEMBL420671</t>
         </is>
       </c>
       <c r="B414" t="n">
         <v>1</v>
       </c>
       <c r="C414" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D414" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>CHEMBL410448</t>
+          <t>CHEMBL421138</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -10228,7 +10228,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>CHEMBL410462</t>
+          <t>CHEMBL410448</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -10244,7 +10244,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>CHEMBL411930</t>
+          <t>CHEMBL410462</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -10260,7 +10260,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>CHEMBL417656</t>
+          <t>CHEMBL411930</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -10276,7 +10276,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CHEMBL417844</t>
+          <t>CHEMBL417656</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -10292,7 +10292,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CHEMBL1234777</t>
+          <t>CHEMBL417844</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -10308,7 +10308,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CHEMBL1234797</t>
+          <t>CHEMBL1234777</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -10324,7 +10324,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>CHEMBL1234815</t>
+          <t>CHEMBL1234797</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -10340,7 +10340,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>CHEMBL1234916</t>
+          <t>CHEMBL1234815</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -10356,7 +10356,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>CHEMBL1235084</t>
+          <t>CHEMBL1234916</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -10372,7 +10372,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>CHEMBL1235106</t>
+          <t>CHEMBL1235084</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -10388,7 +10388,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>CHEMBL1235110</t>
+          <t>CHEMBL1235106</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -10404,7 +10404,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>CHEMBL1235136</t>
+          <t>CHEMBL1235110</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -10420,7 +10420,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>CHEMBL1235151</t>
+          <t>CHEMBL1235136</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -10436,7 +10436,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>CHEMBL420311</t>
+          <t>CHEMBL1235151</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -10452,7 +10452,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>CHEMBL425584</t>
+          <t>CHEMBL420311</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -10468,7 +10468,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>CHEMBL425646</t>
+          <t>CHEMBL425584</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -10484,7 +10484,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>CHEMBL426815</t>
+          <t>CHEMBL425646</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -10500,7 +10500,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>CHEMBL427896</t>
+          <t>CHEMBL426815</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -10516,7 +10516,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CHEMBL4280145</t>
+          <t>CHEMBL427896</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -10532,119 +10532,119 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CHEMBL428462</t>
+          <t>CHEMBL4280145</t>
         </is>
       </c>
       <c r="B435" t="n">
         <v>1</v>
       </c>
       <c r="C435" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D435" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CHEMBL1234640</t>
+          <t>CHEMBL428462</t>
         </is>
       </c>
       <c r="B436" t="n">
         <v>1</v>
       </c>
       <c r="C436" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D436" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>CHEMBL1234669</t>
+          <t>CHEMBL1234640</t>
         </is>
       </c>
       <c r="B437" t="n">
         <v>1</v>
       </c>
       <c r="C437" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D437" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CHEMBL432359</t>
+          <t>CHEMBL1234669</t>
         </is>
       </c>
       <c r="B438" t="n">
         <v>1</v>
       </c>
       <c r="C438" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D438" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>CHEMBL433501</t>
+          <t>CHEMBL432359</t>
         </is>
       </c>
       <c r="B439" t="n">
         <v>1</v>
       </c>
       <c r="C439" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D439" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>CHEMBL439009</t>
+          <t>CHEMBL433501</t>
         </is>
       </c>
       <c r="B440" t="n">
         <v>1</v>
       </c>
       <c r="C440" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D440" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>CHEMBL1234032</t>
+          <t>CHEMBL439009</t>
         </is>
       </c>
       <c r="B441" t="n">
         <v>1</v>
       </c>
       <c r="C441" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D441" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>CHEMBL1234033</t>
+          <t>CHEMBL1234032</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -10660,23 +10660,23 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>CHEMBL1234048</t>
+          <t>CHEMBL1234033</t>
         </is>
       </c>
       <c r="B443" t="n">
         <v>1</v>
       </c>
       <c r="C443" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D443" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>CHEMBL1234135</t>
+          <t>CHEMBL1234048</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -10692,7 +10692,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>CHEMBL1234162</t>
+          <t>CHEMBL1234135</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -10708,7 +10708,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CHEMBL1234200</t>
+          <t>CHEMBL1234162</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -10724,7 +10724,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>CHEMBL123440</t>
+          <t>CHEMBL1234200</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -10740,7 +10740,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>CHEMBL1234416</t>
+          <t>CHEMBL123440</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -10756,7 +10756,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>CHEMBL1234585</t>
+          <t>CHEMBL1234416</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -10772,7 +10772,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>CHEMBL430879</t>
+          <t>CHEMBL1234585</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -10788,7 +10788,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>CHEMBL436462</t>
+          <t>CHEMBL430879</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -10804,39 +10804,39 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>CHEMBL437508</t>
+          <t>CHEMBL436462</t>
         </is>
       </c>
       <c r="B452" t="n">
         <v>1</v>
       </c>
       <c r="C452" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D452" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>CHEMBL437557</t>
+          <t>CHEMBL437508</t>
         </is>
       </c>
       <c r="B453" t="n">
         <v>1</v>
       </c>
       <c r="C453" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D453" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>CHEMBL437747</t>
+          <t>CHEMBL437557</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -10852,39 +10852,39 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>CHEMBL123368</t>
+          <t>CHEMBL437747</t>
         </is>
       </c>
       <c r="B455" t="n">
         <v>1</v>
       </c>
       <c r="C455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D455" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>CHEMBL1233749</t>
+          <t>CHEMBL123368</t>
         </is>
       </c>
       <c r="B456" t="n">
         <v>1</v>
       </c>
       <c r="C456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D456" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>CHEMBL1233797</t>
+          <t>CHEMBL1233749</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -10900,7 +10900,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>CHEMBL1233881</t>
+          <t>CHEMBL1233797</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -10916,7 +10916,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>CHEMBL1233882</t>
+          <t>CHEMBL1233881</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -10932,7 +10932,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>CHEMBL1233960</t>
+          <t>CHEMBL1233882</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -10948,7 +10948,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>CHEMBL1231778</t>
+          <t>CHEMBL1233960</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -10964,7 +10964,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>CHEMBL1231797</t>
+          <t>CHEMBL1231778</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -10980,7 +10980,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>CHEMBL452289</t>
+          <t>CHEMBL1231797</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -10996,7 +10996,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>CHEMBL452587</t>
+          <t>CHEMBL452289</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -11012,7 +11012,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CHEMBL453620</t>
+          <t>CHEMBL452587</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -11028,7 +11028,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>CHEMBL455271</t>
+          <t>CHEMBL453620</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -11044,7 +11044,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>CHEMBL455333</t>
+          <t>CHEMBL455271</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -11060,7 +11060,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>CHEMBL446435</t>
+          <t>CHEMBL455333</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -11076,39 +11076,39 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>CHEMBL451509</t>
+          <t>CHEMBL446435</t>
         </is>
       </c>
       <c r="B469" t="n">
         <v>1</v>
       </c>
       <c r="C469" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D469" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Selenazole-4-Carboxamide Adenine Dinucleotide</t>
+          <t>CHEMBL451509</t>
         </is>
       </c>
       <c r="B470" t="n">
         <v>1</v>
       </c>
       <c r="C470" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D470" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>CHEMBL1231909</t>
+          <t>Selenazole-4-Carboxamide Adenine Dinucleotide</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -11124,23 +11124,23 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>CHEMBL1232157</t>
+          <t>CHEMBL1231909</t>
         </is>
       </c>
       <c r="B472" t="n">
         <v>1</v>
       </c>
       <c r="C472" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D472" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CHEMBL1232243</t>
+          <t>CHEMBL1232157</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -11156,23 +11156,23 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>CHEMBL1232261</t>
+          <t>CHEMBL1232243</t>
         </is>
       </c>
       <c r="B474" t="n">
         <v>1</v>
       </c>
       <c r="C474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D474" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>CHEMBL1232391</t>
+          <t>CHEMBL1232261</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -11188,7 +11188,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>CHEMBL1232829</t>
+          <t>CHEMBL1232391</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -11204,7 +11204,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>CHEMBL1230661</t>
+          <t>CHEMBL1232829</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -11220,7 +11220,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>CHEMBL1230662</t>
+          <t>CHEMBL1230661</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -11236,7 +11236,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>CHEMBL462228</t>
+          <t>CHEMBL1230662</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -11252,7 +11252,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>CHEMBL462712</t>
+          <t>CHEMBL462228</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -11268,7 +11268,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>CHEMBL455907</t>
+          <t>CHEMBL462712</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -11284,39 +11284,39 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>CHEMBL457530</t>
+          <t>CHEMBL455907</t>
         </is>
       </c>
       <c r="B482" t="n">
         <v>1</v>
       </c>
       <c r="C482" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D482" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>CHEMBL458975</t>
+          <t>CHEMBL457530</t>
         </is>
       </c>
       <c r="B483" t="n">
         <v>1</v>
       </c>
       <c r="C483" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D483" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>CHEMBL459149</t>
+          <t>CHEMBL458975</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -11332,7 +11332,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>CHEMBL46780</t>
+          <t>CHEMBL459149</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -11348,39 +11348,39 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>CHEMBL46817</t>
+          <t>CHEMBL46780</t>
         </is>
       </c>
       <c r="B486" t="n">
         <v>1</v>
       </c>
       <c r="C486" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D486" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>CHEMBL469099</t>
+          <t>CHEMBL46817</t>
         </is>
       </c>
       <c r="B487" t="n">
         <v>1</v>
       </c>
       <c r="C487" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D487" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>CHEMBL470365</t>
+          <t>CHEMBL469099</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -11396,7 +11396,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>CHEMBL460910</t>
+          <t>CHEMBL470365</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -11412,7 +11412,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>CHEMBL460962</t>
+          <t>CHEMBL460910</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -11428,39 +11428,39 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>CHEMBL46148</t>
+          <t>CHEMBL460962</t>
         </is>
       </c>
       <c r="B491" t="n">
         <v>1</v>
       </c>
       <c r="C491" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D491" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>CHEMBL1230763</t>
+          <t>CHEMBL46148</t>
         </is>
       </c>
       <c r="B492" t="n">
         <v>1</v>
       </c>
       <c r="C492" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D492" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>CHEMBL1230893</t>
+          <t>CHEMBL1230763</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -11476,7 +11476,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>CHEMBL1231193</t>
+          <t>CHEMBL1230893</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -11492,7 +11492,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>CHEMBL1231206</t>
+          <t>CHEMBL1231193</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -11508,7 +11508,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>CHEMBL1231453</t>
+          <t>CHEMBL1231206</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -11524,7 +11524,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>CHEMBL1231533</t>
+          <t>CHEMBL1231453</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -11540,7 +11540,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>CHEMBL1231592</t>
+          <t>CHEMBL1231533</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -11556,7 +11556,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>CHEMBL1231666</t>
+          <t>CHEMBL1231592</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -11572,7 +11572,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>CHEMBL1229677</t>
+          <t>CHEMBL1231666</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -11588,7 +11588,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>CHEMBL1229801</t>
+          <t>CHEMBL1229677</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -11604,7 +11604,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>CHEMBL472193</t>
+          <t>CHEMBL1229801</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -11620,39 +11620,39 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>CHEMBL47302</t>
+          <t>CHEMBL472193</t>
         </is>
       </c>
       <c r="B503" t="n">
         <v>1</v>
       </c>
       <c r="C503" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D503" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>CHEMBL473922</t>
+          <t>CHEMBL47302</t>
         </is>
       </c>
       <c r="B504" t="n">
         <v>1</v>
       </c>
       <c r="C504" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D504" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>CHEMBL475814</t>
+          <t>CHEMBL473922</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -11668,7 +11668,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>CHEMBL466496</t>
+          <t>CHEMBL475814</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -11684,7 +11684,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>CHEMBL1230670</t>
+          <t>CHEMBL466496</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -11700,7 +11700,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>CHEMBL486921</t>
+          <t>CHEMBL1230670</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -11716,7 +11716,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>CHEMBL478464</t>
+          <t>CHEMBL486921</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -11732,39 +11732,39 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>CHEMBL479014</t>
+          <t>CHEMBL478464</t>
         </is>
       </c>
       <c r="B510" t="n">
         <v>1</v>
       </c>
       <c r="C510" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D510" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>CHEMBL48109</t>
+          <t>CHEMBL479014</t>
         </is>
       </c>
       <c r="B511" t="n">
         <v>1</v>
       </c>
       <c r="C511" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D511" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>CHEMBL482193</t>
+          <t>CHEMBL48109</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -11780,23 +11780,23 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>CHEMBL482708</t>
+          <t>CHEMBL482193</t>
         </is>
       </c>
       <c r="B513" t="n">
         <v>1</v>
       </c>
       <c r="C513" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D513" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>CHEMBL1230044</t>
+          <t>CHEMBL482708</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -11812,7 +11812,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>CHEMBL1230062</t>
+          <t>CHEMBL1230044</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -11828,7 +11828,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>CHEMBL1230270</t>
+          <t>CHEMBL1230062</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -11844,7 +11844,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>CHEMBL1230612</t>
+          <t>CHEMBL1230270</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -11860,7 +11860,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>CHEMBL1230658</t>
+          <t>CHEMBL1230612</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -11876,7 +11876,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>CHEMBL121790</t>
+          <t>CHEMBL1230658</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -11892,7 +11892,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>CHEMBL483716</t>
+          <t>CHEMBL121790</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -11908,7 +11908,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>CHEMBL483849</t>
+          <t>CHEMBL483716</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -11924,7 +11924,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>CHEMBL483995</t>
+          <t>CHEMBL483849</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -11940,7 +11940,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>CHEMBL484726</t>
+          <t>CHEMBL483995</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -11956,7 +11956,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>CHEMBL484780</t>
+          <t>CHEMBL484726</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -11972,7 +11972,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>CHEMBL485323</t>
+          <t>CHEMBL484780</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -11988,7 +11988,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>CHEMBL485835</t>
+          <t>CHEMBL485323</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -12004,7 +12004,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>CHEMBL485945</t>
+          <t>CHEMBL485835</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -12020,7 +12020,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>CHEMBL487431</t>
+          <t>CHEMBL485945</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -12036,7 +12036,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>CHEMBL48813</t>
+          <t>CHEMBL487431</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -12052,7 +12052,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>CHEMBL490730</t>
+          <t>CHEMBL48813</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -12068,7 +12068,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>CHEMBL490814</t>
+          <t>CHEMBL490730</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -12084,7 +12084,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>CHEMBL490866</t>
+          <t>CHEMBL490814</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -12100,7 +12100,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>CHEMBL491429</t>
+          <t>CHEMBL490866</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -12116,7 +12116,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>CHEMBL483161</t>
+          <t>CHEMBL491429</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -12132,7 +12132,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>CHEMBL1229851</t>
+          <t>CHEMBL483161</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -12148,7 +12148,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>CHEMBL1229855</t>
+          <t>CHEMBL1229851</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -12164,7 +12164,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>CHEMBL1229914</t>
+          <t>CHEMBL1229855</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -12180,7 +12180,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>CHEMBL1229989</t>
+          <t>CHEMBL1229914</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -12196,7 +12196,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>CHEMBL1230016</t>
+          <t>CHEMBL1229989</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -12212,7 +12212,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>CHEMBL506972</t>
+          <t>CHEMBL1230016</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -12228,7 +12228,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>CHEMBL509101</t>
+          <t>CHEMBL506972</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -12244,7 +12244,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>CHEMBL493986</t>
+          <t>CHEMBL509101</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -12260,7 +12260,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>CHEMBL495597</t>
+          <t>CHEMBL493986</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -12276,7 +12276,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>CHEMBL495758</t>
+          <t>CHEMBL495597</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -12292,39 +12292,39 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>CHEMBL496879</t>
+          <t>CHEMBL495758</t>
         </is>
       </c>
       <c r="B545" t="n">
         <v>1</v>
       </c>
       <c r="C545" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D545" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>CHEMBL1221657</t>
+          <t>CHEMBL496879</t>
         </is>
       </c>
       <c r="B546" t="n">
         <v>1</v>
       </c>
       <c r="C546" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D546" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>CHEMBL1221659</t>
+          <t>CHEMBL1221657</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -12340,7 +12340,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>CHEMBL1221660</t>
+          <t>CHEMBL1221659</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -12356,7 +12356,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>CHEMBL1221699</t>
+          <t>CHEMBL1221660</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -12372,7 +12372,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>CHEMBL1221702</t>
+          <t>CHEMBL1221699</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -12388,7 +12388,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>CHEMBL1229525</t>
+          <t>CHEMBL1221702</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -12404,39 +12404,39 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>CHEMBL1229535</t>
+          <t>CHEMBL1229525</t>
         </is>
       </c>
       <c r="B552" t="n">
         <v>1</v>
       </c>
       <c r="C552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D552" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>CHEMBL120708</t>
+          <t>CHEMBL1229535</t>
         </is>
       </c>
       <c r="B553" t="n">
         <v>1</v>
       </c>
       <c r="C553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D553" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>CHEMBL503090</t>
+          <t>CHEMBL120708</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -12452,7 +12452,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>CHEMBL504805</t>
+          <t>CHEMBL503090</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -12468,39 +12468,39 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>CHEMBL510539</t>
+          <t>CHEMBL504805</t>
         </is>
       </c>
       <c r="B556" t="n">
         <v>1</v>
       </c>
       <c r="C556" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D556" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>CHEMBL512172</t>
+          <t>CHEMBL510539</t>
         </is>
       </c>
       <c r="B557" t="n">
         <v>1</v>
       </c>
       <c r="C557" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D557" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>CHEMBL512283</t>
+          <t>CHEMBL512172</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -12516,7 +12516,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>CHEMBL513225</t>
+          <t>CHEMBL512283</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -12532,7 +12532,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>CHEMBL513425</t>
+          <t>CHEMBL513225</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -12548,39 +12548,39 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>CHEMBL121941</t>
+          <t>CHEMBL513425</t>
         </is>
       </c>
       <c r="B561" t="n">
         <v>1</v>
       </c>
       <c r="C561" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D561" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>CHEMBL527018</t>
+          <t>CHEMBL121941</t>
         </is>
       </c>
       <c r="B562" t="n">
         <v>1</v>
       </c>
       <c r="C562" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D562" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>CHEMBL527066</t>
+          <t>CHEMBL527018</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -12596,23 +12596,23 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>CHEMBL516357</t>
+          <t>CHEMBL527066</t>
         </is>
       </c>
       <c r="B564" t="n">
         <v>1</v>
       </c>
       <c r="C564" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D564" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>CHEMBL518800</t>
+          <t>CHEMBL516357</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -12628,23 +12628,23 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>CHEMBL519160</t>
+          <t>CHEMBL518800</t>
         </is>
       </c>
       <c r="B566" t="n">
         <v>1</v>
       </c>
       <c r="C566" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D566" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>CHEMBL519939</t>
+          <t>CHEMBL519160</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -12660,7 +12660,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>CHEMBL521105</t>
+          <t>CHEMBL519939</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -12676,7 +12676,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>CHEMBL521703</t>
+          <t>CHEMBL521105</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -12692,7 +12692,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>CHEMBL509485</t>
+          <t>CHEMBL521703</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -12708,7 +12708,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>CHEMBL1210221</t>
+          <t>CHEMBL509485</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -12724,7 +12724,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>CHEMBL121291</t>
+          <t>CHEMBL1210221</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -12740,7 +12740,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>CHEMBL120293</t>
+          <t>CHEMBL121291</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -12756,23 +12756,23 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>CHEMBL1204628</t>
+          <t>CHEMBL120293</t>
         </is>
       </c>
       <c r="B574" t="n">
         <v>1</v>
       </c>
       <c r="C574" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D574" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>CHEMBL1205452</t>
+          <t>CHEMBL1204628</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -12788,39 +12788,39 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>CHEMBL1205948</t>
+          <t>CHEMBL1205452</t>
         </is>
       </c>
       <c r="B576" t="n">
         <v>1</v>
       </c>
       <c r="C576" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D576" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>CHEMBL522891</t>
+          <t>CHEMBL1205948</t>
         </is>
       </c>
       <c r="B577" t="n">
         <v>1</v>
       </c>
       <c r="C577" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D577" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>CHEMBL525194</t>
+          <t>CHEMBL522891</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -12836,23 +12836,23 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>CHEMBL537968</t>
+          <t>CHEMBL525194</t>
         </is>
       </c>
       <c r="B579" t="n">
         <v>1</v>
       </c>
       <c r="C579" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D579" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>CHEMBL538937</t>
+          <t>CHEMBL537968</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -12868,7 +12868,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>CHEMBL539906</t>
+          <t>CHEMBL538937</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -12884,23 +12884,23 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>CHEMBL522387</t>
+          <t>CHEMBL539906</t>
         </is>
       </c>
       <c r="B582" t="n">
         <v>1</v>
       </c>
       <c r="C582" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D582" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>CHEMBL54277</t>
+          <t>CHEMBL522387</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -12916,23 +12916,23 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>CHEMBL54481</t>
+          <t>CHEMBL54277</t>
         </is>
       </c>
       <c r="B584" t="n">
         <v>1</v>
       </c>
       <c r="C584" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D584" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>CHEMBL549340</t>
+          <t>CHEMBL54481</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -12948,7 +12948,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>CHEMBL549385</t>
+          <t>CHEMBL549340</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -12964,7 +12964,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>CHEMBL549906</t>
+          <t>CHEMBL549385</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -12980,7 +12980,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>CHEMBL550453</t>
+          <t>CHEMBL549906</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -12996,7 +12996,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>CHEMBL563327</t>
+          <t>CHEMBL550453</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -13012,7 +13012,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>CHEMBL564249</t>
+          <t>CHEMBL563327</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -13028,7 +13028,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>CHEMBL550795</t>
+          <t>CHEMBL564249</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -13044,7 +13044,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>CHEMBL554496</t>
+          <t>CHEMBL550795</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -13060,71 +13060,71 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>CHEMBL555205</t>
+          <t>CHEMBL554496</t>
         </is>
       </c>
       <c r="B593" t="n">
         <v>1</v>
       </c>
       <c r="C593" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D593" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>CHEMBL557915</t>
+          <t>CHEMBL555205</t>
         </is>
       </c>
       <c r="B594" t="n">
         <v>1</v>
       </c>
       <c r="C594" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D594" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>CHEMBL560739</t>
+          <t>CHEMBL557915</t>
         </is>
       </c>
       <c r="B595" t="n">
         <v>1</v>
       </c>
       <c r="C595" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D595" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>CHEMBL561318</t>
+          <t>CHEMBL560739</t>
         </is>
       </c>
       <c r="B596" t="n">
         <v>1</v>
       </c>
       <c r="C596" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D596" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>CHEMBL561540</t>
+          <t>CHEMBL561318</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -13140,7 +13140,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>CHEMBL561660</t>
+          <t>CHEMBL561540</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -13156,7 +13156,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>CHEMBL562314</t>
+          <t>CHEMBL561660</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -13172,7 +13172,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>CHEMBL562743</t>
+          <t>CHEMBL562314</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -13188,7 +13188,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>CHEMBL563168</t>
+          <t>CHEMBL562743</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -13204,7 +13204,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>CHEMBL570533</t>
+          <t>CHEMBL563168</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -13220,7 +13220,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>CHEMBL570537</t>
+          <t>CHEMBL570533</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -13236,7 +13236,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>CHEMBL577144</t>
+          <t>CHEMBL570537</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -13252,7 +13252,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>CHEMBL582887</t>
+          <t>CHEMBL577144</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -13268,71 +13268,71 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>NIACIN</t>
+          <t>CHEMBL582887</t>
         </is>
       </c>
       <c r="B606" t="n">
         <v>1</v>
       </c>
       <c r="C606" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D606" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>CHEMBL573819</t>
+          <t>NIACIN</t>
         </is>
       </c>
       <c r="B607" t="n">
         <v>1</v>
       </c>
       <c r="C607" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D607" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>CHEMBL62836</t>
+          <t>CHEMBL573819</t>
         </is>
       </c>
       <c r="B608" t="n">
         <v>1</v>
       </c>
       <c r="C608" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D608" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>CHEMBL62897</t>
+          <t>CHEMBL62836</t>
         </is>
       </c>
       <c r="B609" t="n">
         <v>1</v>
       </c>
       <c r="C609" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D609" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>CHEMBL603367</t>
+          <t>CHEMBL62897</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -13348,7 +13348,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>CALCIUM CHLORIDE</t>
+          <t>CHEMBL603367</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -13364,39 +13364,39 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>NITRIC OXIDE</t>
+          <t>CALCIUM CHLORIDE</t>
         </is>
       </c>
       <c r="B612" t="n">
         <v>1</v>
       </c>
       <c r="C612" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D612" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>CHEMBL63859</t>
+          <t>NITRIC OXIDE</t>
         </is>
       </c>
       <c r="B613" t="n">
         <v>1</v>
       </c>
       <c r="C613" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D613" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>CHEMBL63895</t>
+          <t>CHEMBL63859</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -13412,7 +13412,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>CHEMBL1198130</t>
+          <t>CHEMBL63895</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -13428,39 +13428,39 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>CHEMBL1198138</t>
+          <t>CHEMBL1198130</t>
         </is>
       </c>
       <c r="B616" t="n">
         <v>1</v>
       </c>
       <c r="C616" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D616" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>CHEMBL1198147</t>
+          <t>CHEMBL1198138</t>
         </is>
       </c>
       <c r="B617" t="n">
         <v>1</v>
       </c>
       <c r="C617" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D617" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>CHEMBL1198148</t>
+          <t>CHEMBL1198147</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -13476,7 +13476,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>CHEMBL1198191</t>
+          <t>CHEMBL1198148</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -13492,7 +13492,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>CHEMBL1198500</t>
+          <t>CHEMBL1198191</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -13508,39 +13508,39 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>CHEMBL1198650</t>
+          <t>CHEMBL1198500</t>
         </is>
       </c>
       <c r="B621" t="n">
         <v>1</v>
       </c>
       <c r="C621" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D621" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>CHEMBL1184499</t>
+          <t>CHEMBL1198650</t>
         </is>
       </c>
       <c r="B622" t="n">
         <v>1</v>
       </c>
       <c r="C622" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D622" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>CHEMBL64934</t>
+          <t>CHEMBL1184499</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -13556,7 +13556,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>CHEMBL65273</t>
+          <t>CHEMBL64934</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -13572,7 +13572,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>CHEMBL119084</t>
+          <t>CHEMBL65273</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -13588,7 +13588,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>CHEMBL1194345</t>
+          <t>CHEMBL119084</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -13604,7 +13604,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>CHEMBL119489</t>
+          <t>CHEMBL1194345</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -13620,39 +13620,39 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>CHEMBL6685</t>
+          <t>CHEMBL119489</t>
         </is>
       </c>
       <c r="B628" t="n">
         <v>1</v>
       </c>
       <c r="C628" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D628" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>CHEMBL66907</t>
+          <t>CHEMBL6685</t>
         </is>
       </c>
       <c r="B629" t="n">
         <v>1</v>
       </c>
       <c r="C629" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D629" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>CHEMBL67158</t>
+          <t>CHEMBL66907</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -13668,7 +13668,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>CHEMBL1197118</t>
+          <t>CHEMBL67158</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -13684,7 +13684,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>CHEMBL117869</t>
+          <t>CHEMBL1197118</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -13700,7 +13700,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>CHEMBL1161221</t>
+          <t>CHEMBL117869</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -13716,7 +13716,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>CHEMBL1185001</t>
+          <t>CHEMBL1161221</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -13732,7 +13732,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>CHEMBL1185242</t>
+          <t>CHEMBL1185001</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -13748,7 +13748,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>CHEMBL1186230</t>
+          <t>CHEMBL1185242</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -13764,7 +13764,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>CHEMBL116597</t>
+          <t>CHEMBL1186230</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -13780,39 +13780,39 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>CHEMBL71360</t>
+          <t>CHEMBL116597</t>
         </is>
       </c>
       <c r="B638" t="n">
         <v>1</v>
       </c>
       <c r="C638" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D638" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>CHEMBL71611</t>
+          <t>CHEMBL71360</t>
         </is>
       </c>
       <c r="B639" t="n">
         <v>1</v>
       </c>
       <c r="C639" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D639" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>CHEMBL1173</t>
+          <t>CHEMBL71611</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -13828,7 +13828,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>CHEMBL117651</t>
+          <t>CHEMBL1173</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -13844,7 +13844,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>CHEMBL117658</t>
+          <t>CHEMBL117651</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -13860,7 +13860,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>CHEMBL1160756</t>
+          <t>CHEMBL117658</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -13876,7 +13876,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>CHEMBL1161222</t>
+          <t>CHEMBL1160756</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -13892,7 +13892,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>CHEMBL1163074</t>
+          <t>CHEMBL1161222</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -13908,7 +13908,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>CHEMBL1163086</t>
+          <t>CHEMBL1163074</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -13924,7 +13924,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>CHEMBL78755</t>
+          <t>CHEMBL1163086</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -13940,7 +13940,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>CHEMBL75691</t>
+          <t>CHEMBL78755</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -13956,71 +13956,71 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>CHEMBL76029</t>
+          <t>CHEMBL75691</t>
         </is>
       </c>
       <c r="B649" t="n">
         <v>1</v>
       </c>
       <c r="C649" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D649" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>CHEMBL72006</t>
+          <t>CHEMBL76029</t>
         </is>
       </c>
       <c r="B650" t="n">
         <v>1</v>
       </c>
       <c r="C650" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D650" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>CHEMBL115220</t>
+          <t>CHEMBL72006</t>
         </is>
       </c>
       <c r="B651" t="n">
         <v>1</v>
       </c>
       <c r="C651" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D651" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>CHEMBL115357</t>
+          <t>CHEMBL115220</t>
         </is>
       </c>
       <c r="B652" t="n">
         <v>1</v>
       </c>
       <c r="C652" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D652" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>CHEMBL1160597</t>
+          <t>CHEMBL115357</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -14036,7 +14036,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>CHEMBL1160619</t>
+          <t>CHEMBL1160597</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -14052,7 +14052,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>CHEMBL112953</t>
+          <t>CHEMBL1160619</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -14068,7 +14068,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>CHEMBL113194</t>
+          <t>CHEMBL112953</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -14084,7 +14084,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>CHEMBL113948</t>
+          <t>CHEMBL113194</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -14100,7 +14100,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>CHEMBL77961</t>
+          <t>CHEMBL113948</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -14116,7 +14116,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>CHEMBL78455</t>
+          <t>CHEMBL77961</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -14132,7 +14132,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>CHEMBL111575</t>
+          <t>CHEMBL78455</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -14148,7 +14148,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>CHEMBL81273</t>
+          <t>CHEMBL111575</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -14164,7 +14164,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>CHEMBL112834</t>
+          <t>CHEMBL81273</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -14180,7 +14180,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>CHEMBL112896</t>
+          <t>CHEMBL112834</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -14196,7 +14196,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>CHEMBL83116</t>
+          <t>CHEMBL112896</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -14212,7 +14212,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>CHEMBL83547</t>
+          <t>CHEMBL83116</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -14228,7 +14228,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>CHEMBL109612</t>
+          <t>CHEMBL83547</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -14244,71 +14244,71 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>CHEMBL1098060</t>
+          <t>CHEMBL109612</t>
         </is>
       </c>
       <c r="B667" t="n">
         <v>1</v>
       </c>
       <c r="C667" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D667" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>CHEMBL109822</t>
+          <t>CHEMBL1098060</t>
         </is>
       </c>
       <c r="B668" t="n">
         <v>1</v>
       </c>
       <c r="C668" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D668" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>BIOTIN</t>
+          <t>CHEMBL109822</t>
         </is>
       </c>
       <c r="B669" t="n">
         <v>1</v>
       </c>
       <c r="C669" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D669" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>CHEMBL1088762</t>
+          <t>BIOTIN</t>
         </is>
       </c>
       <c r="B670" t="n">
         <v>1</v>
       </c>
       <c r="C670" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D670" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>CHEMBL1090777</t>
+          <t>CHEMBL1088762</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -14324,7 +14324,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>CHEMBL1092830</t>
+          <t>CHEMBL1090777</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -14340,7 +14340,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>CHEMBL109367</t>
+          <t>CHEMBL1092830</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -14356,7 +14356,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>CHEMBL86554</t>
+          <t>CHEMBL109367</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -14372,7 +14372,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>CHEMBL86658</t>
+          <t>CHEMBL86554</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -14388,7 +14388,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>CHEMBL87580</t>
+          <t>CHEMBL86658</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -14404,7 +14404,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>CHEMBL108483</t>
+          <t>CHEMBL87580</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -14420,7 +14420,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>CHEMBL1088749</t>
+          <t>CHEMBL108483</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -14436,7 +14436,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>CHEMBL92404</t>
+          <t>CHEMBL1088749</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -14452,7 +14452,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>CHEMBL92567</t>
+          <t>CHEMBL92404</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -14468,7 +14468,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>CHEMBL93247</t>
+          <t>CHEMBL92567</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -14484,7 +14484,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>CHEMBL1081312</t>
+          <t>CHEMBL93247</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -14500,7 +14500,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>CHEMBL1082738</t>
+          <t>CHEMBL1081312</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -14516,7 +14516,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>CHEMBL1083185</t>
+          <t>CHEMBL1082738</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -14532,7 +14532,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>CHEMBL1084102</t>
+          <t>CHEMBL1083185</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -14548,7 +14548,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>CHEMBL1084625</t>
+          <t>CHEMBL1084102</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -14564,7 +14564,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>CHEMBL100109</t>
+          <t>CHEMBL1084625</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -14580,7 +14580,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>CHEMBL99447</t>
+          <t>CHEMBL100109</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -14596,7 +14596,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>CHEMBL104166</t>
+          <t>CHEMBL99447</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -14612,7 +14612,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>CHOLECALCIFEROL</t>
+          <t>CHEMBL104166</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -14628,7 +14628,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>CHEMBL104937</t>
+          <t>CHOLECALCIFEROL</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -14644,7 +14644,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>CHEMBL196526</t>
+          <t>CHEMBL104937</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -14660,7 +14660,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>CHEMBL191060</t>
+          <t>CHEMBL196526</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -14676,48 +14676,64 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>CHEMBL101801</t>
+          <t>CHEMBL191060</t>
         </is>
       </c>
       <c r="B694" t="n">
         <v>1</v>
       </c>
       <c r="C694" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D694" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>PYRIDOXAL</t>
+          <t>CHEMBL101801</t>
         </is>
       </c>
       <c r="B695" t="n">
         <v>1</v>
       </c>
       <c r="C695" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D695" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
+          <t>PYRIDOXAL</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>1</v>
+      </c>
+      <c r="C696" t="n">
+        <v>1</v>
+      </c>
+      <c r="D696" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
           <t>CHEMBL103043</t>
         </is>
       </c>
-      <c r="B696" t="n">
-        <v>1</v>
-      </c>
-      <c r="C696" t="n">
-        <v>1</v>
-      </c>
-      <c r="D696" t="n">
+      <c r="B697" t="n">
+        <v>1</v>
+      </c>
+      <c r="C697" t="n">
+        <v>1</v>
+      </c>
+      <c r="D697" t="n">
         <v>1</v>
       </c>
     </row>
